--- a/public/sampleData.xlsx
+++ b/public/sampleData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U45555\IT-dashboard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C909D23-AAC8-41ED-B145-C6D075F43069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484163C0-9EB3-4ED8-9F45-DFA6A58DBD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{724309DC-2642-42C3-9093-42F88D91BE1B}"/>
   </bookViews>
@@ -4923,6 +4923,7 @@
     <col min="12" max="12" width="23.81640625" customWidth="1"/>
     <col min="13" max="13" width="28.81640625" customWidth="1"/>
     <col min="14" max="14" width="22.36328125" customWidth="1"/>
+    <col min="15" max="15" width="17.453125" customWidth="1"/>
     <col min="16" max="16" width="20.1796875" customWidth="1"/>
     <col min="22" max="22" width="26.08984375" customWidth="1"/>
     <col min="23" max="23" width="17.90625" customWidth="1"/>
@@ -4930,11 +4931,21 @@
     <col min="27" max="27" width="22.453125" customWidth="1"/>
     <col min="36" max="36" width="16.26953125" customWidth="1"/>
     <col min="37" max="37" width="15.08984375" customWidth="1"/>
+    <col min="54" max="54" width="26.36328125" customWidth="1"/>
     <col min="56" max="56" width="22.7265625" customWidth="1"/>
+    <col min="57" max="57" width="29.36328125" customWidth="1"/>
     <col min="59" max="59" width="19.7265625" customWidth="1"/>
     <col min="61" max="61" width="24.08984375" customWidth="1"/>
     <col min="66" max="66" width="26.54296875" customWidth="1"/>
-    <col min="71" max="71" width="22.6328125" customWidth="1"/>
+    <col min="71" max="71" width="44.7265625" customWidth="1"/>
+    <col min="72" max="72" width="40.1796875" customWidth="1"/>
+    <col min="73" max="73" width="38.81640625" customWidth="1"/>
+    <col min="75" max="75" width="27.6328125" customWidth="1"/>
+    <col min="76" max="76" width="33.6328125" customWidth="1"/>
+    <col min="77" max="78" width="37.453125" customWidth="1"/>
+    <col min="79" max="79" width="36.36328125" customWidth="1"/>
+    <col min="80" max="80" width="36.26953125" customWidth="1"/>
+    <col min="81" max="81" width="33.453125" customWidth="1"/>
     <col min="85" max="85" width="22.7265625" customWidth="1"/>
     <col min="86" max="86" width="24.54296875" customWidth="1"/>
     <col min="89" max="89" width="16" customWidth="1"/>

--- a/public/sampleData.xlsx
+++ b/public/sampleData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U45555\IT-dashboard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484163C0-9EB3-4ED8-9F45-DFA6A58DBD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5779CB-5239-47B8-9FFC-4D36264C58D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{724309DC-2642-42C3-9093-42F88D91BE1B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11431" uniqueCount="1458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11431" uniqueCount="1464">
   <si>
     <t>Contract Request ID</t>
   </si>
@@ -4413,6 +4413,24 @@
   </si>
   <si>
     <t>19/6/2025</t>
+  </si>
+  <si>
+    <t>2025-Agosto</t>
+  </si>
+  <si>
+    <t>2025-Octubre</t>
+  </si>
+  <si>
+    <t>2025-Julio</t>
+  </si>
+  <si>
+    <t>2025-Febrero</t>
+  </si>
+  <si>
+    <t>2025-Marzo</t>
+  </si>
+  <si>
+    <t>2025-April</t>
   </si>
 </sst>
 </file>
@@ -4925,6 +4943,8 @@
     <col min="14" max="14" width="22.36328125" customWidth="1"/>
     <col min="15" max="15" width="17.453125" customWidth="1"/>
     <col min="16" max="16" width="20.1796875" customWidth="1"/>
+    <col min="18" max="18" width="31.7265625" customWidth="1"/>
+    <col min="19" max="19" width="15" customWidth="1"/>
     <col min="22" max="22" width="26.08984375" customWidth="1"/>
     <col min="23" max="23" width="17.90625" customWidth="1"/>
     <col min="26" max="26" width="20.26953125" customWidth="1"/>
@@ -5537,7 +5557,7 @@
         <v>2025</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>1313</v>
+        <v>1462</v>
       </c>
       <c r="T3" s="15" t="s">
         <v>1314</v>
@@ -5797,8 +5817,8 @@
       <c r="R4" s="12">
         <v>2025</v>
       </c>
-      <c r="S4" s="12" t="s">
-        <v>1313</v>
+      <c r="S4" s="15" t="s">
+        <v>1462</v>
       </c>
       <c r="T4" s="12" t="s">
         <v>1314</v>
@@ -6059,7 +6079,7 @@
         <v>2025</v>
       </c>
       <c r="S5" s="15" t="s">
-        <v>1313</v>
+        <v>1462</v>
       </c>
       <c r="T5" s="15" t="s">
         <v>1314</v>
@@ -6315,8 +6335,8 @@
       <c r="R6" s="12">
         <v>2025</v>
       </c>
-      <c r="S6" s="12" t="s">
-        <v>1313</v>
+      <c r="S6" s="15" t="s">
+        <v>1462</v>
       </c>
       <c r="T6" s="12" t="s">
         <v>1314</v>
@@ -6831,8 +6851,8 @@
       <c r="R8" s="12">
         <v>2025</v>
       </c>
-      <c r="S8" s="12" t="s">
-        <v>1313</v>
+      <c r="S8" s="15" t="s">
+        <v>1462</v>
       </c>
       <c r="T8" s="12" t="s">
         <v>1314</v>
@@ -13562,7 +13582,7 @@
         <v>2025</v>
       </c>
       <c r="S34" s="12" t="s">
-        <v>1313</v>
+        <v>1458</v>
       </c>
       <c r="T34" s="12" t="s">
         <v>1314</v>
@@ -15618,7 +15638,7 @@
         <v>2025</v>
       </c>
       <c r="S42" s="12" t="s">
-        <v>1313</v>
+        <v>1461</v>
       </c>
       <c r="T42" s="12" t="s">
         <v>1314</v>
@@ -15878,8 +15898,8 @@
       <c r="R43" s="12">
         <v>2025</v>
       </c>
-      <c r="S43" s="15" t="s">
-        <v>1313</v>
+      <c r="S43" s="12" t="s">
+        <v>1461</v>
       </c>
       <c r="T43" s="15" t="s">
         <v>1314</v>
@@ -16140,7 +16160,7 @@
         <v>2025</v>
       </c>
       <c r="S44" s="12" t="s">
-        <v>1313</v>
+        <v>1461</v>
       </c>
       <c r="T44" s="12" t="s">
         <v>1314</v>
@@ -16396,8 +16416,8 @@
       <c r="R45" s="12">
         <v>2025</v>
       </c>
-      <c r="S45" s="15" t="s">
-        <v>1313</v>
+      <c r="S45" s="12" t="s">
+        <v>1461</v>
       </c>
       <c r="T45" s="15" t="s">
         <v>1314</v>
@@ -16658,7 +16678,7 @@
         <v>2025</v>
       </c>
       <c r="S46" s="12" t="s">
-        <v>1313</v>
+        <v>1461</v>
       </c>
       <c r="T46" s="12" t="s">
         <v>1314</v>
@@ -16916,8 +16936,8 @@
       <c r="R47" s="12">
         <v>2025</v>
       </c>
-      <c r="S47" s="15" t="s">
-        <v>1313</v>
+      <c r="S47" s="12" t="s">
+        <v>1461</v>
       </c>
       <c r="T47" s="15" t="s">
         <v>1314</v>
@@ -17176,7 +17196,7 @@
         <v>2025</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>1313</v>
+        <v>1461</v>
       </c>
       <c r="T48" s="12" t="s">
         <v>1314</v>
@@ -17436,8 +17456,8 @@
       <c r="R49" s="12">
         <v>2025</v>
       </c>
-      <c r="S49" s="15" t="s">
-        <v>1313</v>
+      <c r="S49" s="12" t="s">
+        <v>1461</v>
       </c>
       <c r="T49" s="15" t="s">
         <v>1314</v>
@@ -17696,7 +17716,7 @@
         <v>2025</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>1313</v>
+        <v>1459</v>
       </c>
       <c r="T50" s="12" t="s">
         <v>1288</v>
@@ -17954,8 +17974,8 @@
       <c r="R51" s="12">
         <v>2025</v>
       </c>
-      <c r="S51" s="15" t="s">
-        <v>1313</v>
+      <c r="S51" s="12" t="s">
+        <v>1459</v>
       </c>
       <c r="T51" s="15" t="s">
         <v>1314</v>
@@ -18212,7 +18232,7 @@
         <v>2025</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>1313</v>
+        <v>1459</v>
       </c>
       <c r="T52" s="12" t="s">
         <v>1314</v>
@@ -18468,8 +18488,8 @@
       <c r="R53" s="12">
         <v>2025</v>
       </c>
-      <c r="S53" s="15" t="s">
-        <v>1313</v>
+      <c r="S53" s="12" t="s">
+        <v>1459</v>
       </c>
       <c r="T53" s="15" t="s">
         <v>1314</v>
@@ -18730,7 +18750,7 @@
         <v>2025</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>1313</v>
+        <v>1459</v>
       </c>
       <c r="T54" s="12" t="s">
         <v>1314</v>
@@ -18990,8 +19010,8 @@
       <c r="R55" s="12">
         <v>2025</v>
       </c>
-      <c r="S55" s="15" t="s">
-        <v>1313</v>
+      <c r="S55" s="12" t="s">
+        <v>1459</v>
       </c>
       <c r="T55" s="15" t="s">
         <v>1314</v>
@@ -19246,7 +19266,7 @@
         <v>2025</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>1313</v>
+        <v>1459</v>
       </c>
       <c r="T56" s="12" t="s">
         <v>1314</v>
@@ -19500,8 +19520,8 @@
       <c r="R57" s="12">
         <v>2025</v>
       </c>
-      <c r="S57" s="15" t="s">
-        <v>1313</v>
+      <c r="S57" s="12" t="s">
+        <v>1459</v>
       </c>
       <c r="T57" s="15" t="s">
         <v>1314</v>
@@ -19762,7 +19782,7 @@
         <v>2025</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>1313</v>
+        <v>1459</v>
       </c>
       <c r="T58" s="12" t="s">
         <v>1314</v>
@@ -22856,7 +22876,7 @@
         <v>2025</v>
       </c>
       <c r="S70" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T70" s="12" t="s">
         <v>1314</v>
@@ -23112,8 +23132,8 @@
       <c r="R71" s="12">
         <v>2025</v>
       </c>
-      <c r="S71" s="15" t="s">
-        <v>1313</v>
+      <c r="S71" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T71" s="15" t="s">
         <v>1314</v>
@@ -23374,7 +23394,7 @@
         <v>2025</v>
       </c>
       <c r="S72" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T72" s="12" t="s">
         <v>1314</v>
@@ -23634,8 +23654,8 @@
       <c r="R73" s="12">
         <v>2025</v>
       </c>
-      <c r="S73" s="15" t="s">
-        <v>1313</v>
+      <c r="S73" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T73" s="15" t="s">
         <v>1288</v>
@@ -23896,7 +23916,7 @@
         <v>2025</v>
       </c>
       <c r="S74" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T74" s="12" t="s">
         <v>1314</v>
@@ -24156,8 +24176,8 @@
       <c r="R75" s="12">
         <v>2025</v>
       </c>
-      <c r="S75" s="15" t="s">
-        <v>1313</v>
+      <c r="S75" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T75" s="15" t="s">
         <v>1314</v>
@@ -24418,7 +24438,7 @@
         <v>2025</v>
       </c>
       <c r="S76" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T76" s="12" t="s">
         <v>1288</v>
@@ -24678,8 +24698,8 @@
       <c r="R77" s="12">
         <v>2025</v>
       </c>
-      <c r="S77" s="15" t="s">
-        <v>1313</v>
+      <c r="S77" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T77" s="15" t="s">
         <v>1288</v>
@@ -24940,7 +24960,7 @@
         <v>2025</v>
       </c>
       <c r="S78" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T78" s="12" t="s">
         <v>1288</v>
@@ -25200,8 +25220,8 @@
       <c r="R79" s="12">
         <v>2025</v>
       </c>
-      <c r="S79" s="15" t="s">
-        <v>1313</v>
+      <c r="S79" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T79" s="15" t="s">
         <v>1288</v>
@@ -25462,7 +25482,7 @@
         <v>2025</v>
       </c>
       <c r="S80" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T80" s="12" t="s">
         <v>1288</v>
@@ -25722,8 +25742,8 @@
       <c r="R81" s="12">
         <v>2025</v>
       </c>
-      <c r="S81" s="15" t="s">
-        <v>1313</v>
+      <c r="S81" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T81" s="15" t="s">
         <v>1288</v>
@@ -25976,7 +25996,7 @@
         <v>2025</v>
       </c>
       <c r="S82" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T82" s="12" t="s">
         <v>1288</v>
@@ -26234,8 +26254,8 @@
       <c r="R83" s="12">
         <v>2025</v>
       </c>
-      <c r="S83" s="15" t="s">
-        <v>1313</v>
+      <c r="S83" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T83" s="15" t="s">
         <v>1288</v>
@@ -26488,7 +26508,7 @@
         <v>2025</v>
       </c>
       <c r="S84" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T84" s="12" t="s">
         <v>1288</v>
@@ -26742,8 +26762,8 @@
       <c r="R85" s="12">
         <v>2025</v>
       </c>
-      <c r="S85" s="15" t="s">
-        <v>1313</v>
+      <c r="S85" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T85" s="15" t="s">
         <v>1314</v>
@@ -27002,7 +27022,7 @@
         <v>2025</v>
       </c>
       <c r="S86" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T86" s="12" t="s">
         <v>1288</v>
@@ -27262,8 +27282,8 @@
       <c r="R87" s="12">
         <v>2025</v>
       </c>
-      <c r="S87" s="15" t="s">
-        <v>1313</v>
+      <c r="S87" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T87" s="15" t="s">
         <v>1314</v>
@@ -27520,7 +27540,7 @@
         <v>2025</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T88" s="12" t="s">
         <v>1288</v>
@@ -27780,8 +27800,8 @@
       <c r="R89" s="12">
         <v>2025</v>
       </c>
-      <c r="S89" s="15" t="s">
-        <v>1313</v>
+      <c r="S89" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T89" s="15" t="s">
         <v>1288</v>
@@ -28040,7 +28060,7 @@
         <v>2025</v>
       </c>
       <c r="S90" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T90" s="12" t="s">
         <v>1288</v>
@@ -28298,8 +28318,8 @@
       <c r="R91" s="12">
         <v>2025</v>
       </c>
-      <c r="S91" s="15" t="s">
-        <v>1313</v>
+      <c r="S91" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T91" s="15" t="s">
         <v>1314</v>
@@ -28560,7 +28580,7 @@
         <v>2025</v>
       </c>
       <c r="S92" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T92" s="12" t="s">
         <v>1288</v>
@@ -28818,8 +28838,8 @@
       <c r="R93" s="12">
         <v>2025</v>
       </c>
-      <c r="S93" s="15" t="s">
-        <v>1313</v>
+      <c r="S93" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T93" s="15" t="s">
         <v>1288</v>
@@ -29080,7 +29100,7 @@
         <v>2025</v>
       </c>
       <c r="S94" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T94" s="12" t="s">
         <v>1288</v>
@@ -29340,8 +29360,8 @@
       <c r="R95" s="12">
         <v>2025</v>
       </c>
-      <c r="S95" s="15" t="s">
-        <v>1313</v>
+      <c r="S95" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T95" s="15" t="s">
         <v>1314</v>
@@ -29602,7 +29622,7 @@
         <v>2025</v>
       </c>
       <c r="S96" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T96" s="12" t="s">
         <v>1314</v>
@@ -29862,8 +29882,8 @@
       <c r="R97" s="12">
         <v>2025</v>
       </c>
-      <c r="S97" s="15" t="s">
-        <v>1313</v>
+      <c r="S97" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T97" s="15" t="s">
         <v>1314</v>
@@ -30116,7 +30136,7 @@
         <v>2025</v>
       </c>
       <c r="S98" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T98" s="12" t="s">
         <v>1288</v>
@@ -30368,8 +30388,8 @@
       <c r="R99" s="12">
         <v>2025</v>
       </c>
-      <c r="S99" s="15" t="s">
-        <v>1313</v>
+      <c r="S99" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T99" s="15" t="s">
         <v>1314</v>
@@ -30630,7 +30650,7 @@
         <v>2025</v>
       </c>
       <c r="S100" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T100" s="12" t="s">
         <v>1314</v>
@@ -30888,8 +30908,8 @@
       <c r="R101" s="12">
         <v>2025</v>
       </c>
-      <c r="S101" s="15" t="s">
-        <v>1313</v>
+      <c r="S101" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T101" s="15" t="s">
         <v>1314</v>
@@ -31150,7 +31170,7 @@
         <v>2025</v>
       </c>
       <c r="S102" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T102" s="12" t="s">
         <v>1288</v>
@@ -31410,8 +31430,8 @@
       <c r="R103" s="12">
         <v>2025</v>
       </c>
-      <c r="S103" s="15" t="s">
-        <v>1313</v>
+      <c r="S103" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T103" s="15" t="s">
         <v>1288</v>
@@ -31666,7 +31686,7 @@
         <v>2025</v>
       </c>
       <c r="S104" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T104" s="12" t="s">
         <v>1288</v>
@@ -31924,8 +31944,8 @@
       <c r="R105" s="12">
         <v>2025</v>
       </c>
-      <c r="S105" s="15" t="s">
-        <v>1313</v>
+      <c r="S105" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T105" s="15" t="s">
         <v>1288</v>
@@ -32180,7 +32200,7 @@
         <v>2025</v>
       </c>
       <c r="S106" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T106" s="12" t="s">
         <v>1288</v>
@@ -32440,8 +32460,8 @@
       <c r="R107" s="12">
         <v>2025</v>
       </c>
-      <c r="S107" s="15" t="s">
-        <v>1313</v>
+      <c r="S107" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T107" s="15" t="s">
         <v>1288</v>
@@ -32696,7 +32716,7 @@
         <v>2025</v>
       </c>
       <c r="S108" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T108" s="12" t="s">
         <v>1288</v>
@@ -32950,8 +32970,8 @@
       <c r="R109" s="12">
         <v>2025</v>
       </c>
-      <c r="S109" s="15" t="s">
-        <v>1313</v>
+      <c r="S109" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T109" s="15" t="s">
         <v>1288</v>
@@ -62566,7 +62586,7 @@
         <v>2025</v>
       </c>
       <c r="S257" s="15" t="s">
-        <v>1313</v>
+        <v>1460</v>
       </c>
       <c r="T257" s="15" t="s">
         <v>1314</v>
@@ -62762,7 +62782,7 @@
         <v>2025</v>
       </c>
       <c r="S258" s="12" t="s">
-        <v>1313</v>
+        <v>1460</v>
       </c>
       <c r="T258" s="12" t="s">
         <v>1314</v>
@@ -62952,7 +62972,7 @@
         <v>2025</v>
       </c>
       <c r="S259" s="15" t="s">
-        <v>1313</v>
+        <v>1460</v>
       </c>
       <c r="T259" s="15" t="s">
         <v>1314</v>
@@ -63150,7 +63170,7 @@
         <v>2025</v>
       </c>
       <c r="S260" s="12" t="s">
-        <v>1313</v>
+        <v>1460</v>
       </c>
       <c r="T260" s="12" t="s">
         <v>1314</v>
@@ -64644,7 +64664,7 @@
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A1:N2 A260:N260 O1:CH1 O2:CK111 O112:BN285" name="All Access Jorge H" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A1:N2 A260:N260 O1:CH1 O112:BN285 O2:CK111" name="All Access Jorge H" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A3:N5" name="All Access Jorge H_1" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A6:N6" name="All Access Jorge H_2" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A7:N9" name="All Access Jorge H_3" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>

--- a/public/sampleData.xlsx
+++ b/public/sampleData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U45555\IT-dashboard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5779CB-5239-47B8-9FFC-4D36264C58D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381E9962-C8DA-4D74-9E65-34D3D81CFB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{724309DC-2642-42C3-9093-42F88D91BE1B}"/>
   </bookViews>
@@ -4944,7 +4944,7 @@
     <col min="15" max="15" width="17.453125" customWidth="1"/>
     <col min="16" max="16" width="20.1796875" customWidth="1"/>
     <col min="18" max="18" width="31.7265625" customWidth="1"/>
-    <col min="19" max="19" width="15" customWidth="1"/>
+    <col min="19" max="19" width="36.6328125" customWidth="1"/>
     <col min="22" max="22" width="26.08984375" customWidth="1"/>
     <col min="23" max="23" width="17.90625" customWidth="1"/>
     <col min="26" max="26" width="20.26953125" customWidth="1"/>

--- a/public/sampleData.xlsx
+++ b/public/sampleData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U45555\IT-dashboard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9568CCAA-D392-41F2-A317-374D8C172E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F400CFB-2AF9-484A-94ED-B8DF0A6BD64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{724309DC-2642-42C3-9093-42F88D91BE1B}"/>
   </bookViews>
@@ -27051,8 +27051,8 @@
       <c r="BK82" s="12">
         <v>1</v>
       </c>
-      <c r="BL82" s="12" t="s">
-        <v>1301</v>
+      <c r="BL82" s="15" t="s">
+        <v>1327</v>
       </c>
       <c r="BM82" s="12" t="s">
         <v>1377</v>
@@ -27311,7 +27311,7 @@
         <v>2</v>
       </c>
       <c r="BL83" s="15" t="s">
-        <v>1301</v>
+        <v>1327</v>
       </c>
       <c r="BM83" s="15" t="s">
         <v>1377</v>
@@ -73286,7 +73286,7 @@
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A1:N2 A260:N260 O1:CH1 O112:BN260 O2:CK111 O273:BN285 I261:BN261 BO112:CG261 I262:CG272 A261:G272" name="All Access Jorge H" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A1:N2 A260:N260 O1:CH1 O112:BN260 O273:BN285 I261:BN261 BO112:CG261 I262:CG272 A261:G272 O2:CK111" name="All Access Jorge H" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A3:N5" name="All Access Jorge H_1" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A6:N6" name="All Access Jorge H_2" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A7:N9" name="All Access Jorge H_3" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>

--- a/public/sampleData.xlsx
+++ b/public/sampleData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U45555\IT-dashboard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2093252F-7A37-4371-A6E9-12DA41261601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D82B5FF-91C6-4D90-9C89-9A24B08035B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{724309DC-2642-42C3-9093-42F88D91BE1B}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$CK$290</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$CK$306</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15059" uniqueCount="1767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16027" uniqueCount="1767">
   <si>
     <t>Contract Request ID</t>
   </si>
@@ -5843,7 +5843,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A45D9DC-E8AF-436A-91D0-388125A4A950}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:CK306"/>
+  <dimension ref="A1:CK326"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.7265625" customWidth="1"/>
@@ -9791,7 +9791,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="16" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>102</v>
       </c>
@@ -20135,7 +20135,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="56" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>298</v>
       </c>
@@ -26090,7 +26090,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="79" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>397</v>
       </c>
@@ -26351,7 +26351,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="80" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="7" t="s">
         <v>401</v>
       </c>
@@ -26612,7 +26612,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="81" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>405</v>
       </c>
@@ -26865,7 +26865,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="82" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A82" s="7" t="s">
         <v>409</v>
       </c>
@@ -59270,7 +59270,7 @@
         <v>787228.2</v>
       </c>
     </row>
-    <row r="211" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A211" s="7" t="s">
         <v>981</v>
       </c>
@@ -61531,7 +61531,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="220" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A220" s="7" t="s">
         <v>1027</v>
       </c>
@@ -68607,7 +68607,7 @@
         <v>787265.2</v>
       </c>
     </row>
-    <row r="248" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A248" s="7" t="s">
         <v>1152</v>
       </c>
@@ -72860,7 +72860,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="265" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" s="2" t="s">
         <v>405</v>
       </c>
@@ -73113,7 +73113,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="266" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>405</v>
       </c>
@@ -73366,7 +73366,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="267" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>405</v>
       </c>
@@ -73619,7 +73619,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="268" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>405</v>
       </c>
@@ -73872,7 +73872,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="269" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>405</v>
       </c>
@@ -74125,7 +74125,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="270" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
         <v>405</v>
       </c>
@@ -74378,7 +74378,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="271" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>405</v>
       </c>
@@ -74631,7 +74631,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="272" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>405</v>
       </c>
@@ -74884,7 +74884,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="273" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>405</v>
       </c>
@@ -75137,7 +75137,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="274" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>405</v>
       </c>
@@ -75390,7 +75390,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="275" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>405</v>
       </c>
@@ -75643,7 +75643,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="276" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>102</v>
       </c>
@@ -75904,7 +75904,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="277" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A277" s="7" t="s">
         <v>409</v>
       </c>
@@ -76163,7 +76163,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="278" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A278" s="7" t="s">
         <v>981</v>
       </c>
@@ -76412,7 +76412,7 @@
         <v>787229.2</v>
       </c>
     </row>
-    <row r="279" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A279" s="7" t="s">
         <v>1027</v>
       </c>
@@ -76657,7 +76657,7 @@
         <v>787238.2</v>
       </c>
     </row>
-    <row r="280" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A280" s="7" t="s">
         <v>1152</v>
       </c>
@@ -76902,7 +76902,7 @@
         <v>787266.2</v>
       </c>
     </row>
-    <row r="281" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>102</v>
       </c>
@@ -77163,7 +77163,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="282" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A282" s="7" t="s">
         <v>409</v>
       </c>
@@ -77422,7 +77422,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="283" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A283" s="7" t="s">
         <v>981</v>
       </c>
@@ -77671,7 +77671,7 @@
         <v>787229.2</v>
       </c>
     </row>
-    <row r="284" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A284" s="7" t="s">
         <v>1027</v>
       </c>
@@ -77916,7 +77916,7 @@
         <v>787238.2</v>
       </c>
     </row>
-    <row r="285" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A285" s="7" t="s">
         <v>1152</v>
       </c>
@@ -78161,7 +78161,7 @@
         <v>787266.2</v>
       </c>
     </row>
-    <row r="286" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
         <v>102</v>
       </c>
@@ -78422,7 +78422,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="287" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A287" s="7" t="s">
         <v>409</v>
       </c>
@@ -78681,7 +78681,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="288" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A288" s="7" t="s">
         <v>981</v>
       </c>
@@ -78930,7 +78930,7 @@
         <v>787229.2</v>
       </c>
     </row>
-    <row r="289" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A289" s="7" t="s">
         <v>1027</v>
       </c>
@@ -79175,7 +79175,7 @@
         <v>787238.2</v>
       </c>
     </row>
-    <row r="290" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A290" s="7" t="s">
         <v>1152</v>
       </c>
@@ -79420,7 +79420,7 @@
         <v>787266.2</v>
       </c>
     </row>
-    <row r="291" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
         <v>405</v>
       </c>
@@ -79673,7 +79673,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="292" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>405</v>
       </c>
@@ -79926,7 +79926,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="293" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
         <v>405</v>
       </c>
@@ -80179,7 +80179,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="294" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
         <v>405</v>
       </c>
@@ -80432,7 +80432,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="295" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
         <v>405</v>
       </c>
@@ -80685,7 +80685,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="296" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
         <v>405</v>
       </c>
@@ -80938,7 +80938,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="297" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>405</v>
       </c>
@@ -81191,7 +81191,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="298" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>405</v>
       </c>
@@ -81444,7 +81444,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="299" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>405</v>
       </c>
@@ -81644,7 +81644,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="300" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
         <v>405</v>
       </c>
@@ -81844,7 +81844,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="301" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
         <v>405</v>
       </c>
@@ -82044,7 +82044,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="302" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" s="2" t="s">
         <v>405</v>
       </c>
@@ -82244,7 +82244,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="303" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" s="2" t="s">
         <v>405</v>
       </c>
@@ -82444,7 +82444,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="304" spans="1:89" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" s="2" t="s">
         <v>405</v>
       </c>
@@ -82644,7 +82644,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="305" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
         <v>405</v>
       </c>
@@ -82844,7 +82844,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="306" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" s="2" t="s">
         <v>405</v>
       </c>
@@ -83042,18 +83042,5054 @@
       </c>
       <c r="BN306" s="19">
         <v>46219</v>
+      </c>
+    </row>
+    <row r="307" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A307" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C307" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E307" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F307" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G307" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H307" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I307" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J307" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K307" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="L307" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M307" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N307" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O307" s="12" t="s">
+        <v>1285</v>
+      </c>
+      <c r="P307" s="13">
+        <v>45807</v>
+      </c>
+      <c r="Q307" s="12" t="s">
+        <v>1286</v>
+      </c>
+      <c r="R307" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S307" s="12" t="s">
+        <v>1287</v>
+      </c>
+      <c r="T307" s="12" t="s">
+        <v>1314</v>
+      </c>
+      <c r="U307" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V307" s="13">
+        <v>45812</v>
+      </c>
+      <c r="W307" s="13">
+        <v>45812</v>
+      </c>
+      <c r="X307" s="12">
+        <v>3</v>
+      </c>
+      <c r="Y307" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z307" s="13">
+        <v>45812</v>
+      </c>
+      <c r="AA307" s="13">
+        <v>45812</v>
+      </c>
+      <c r="AB307" s="12" t="s">
+        <v>1355</v>
+      </c>
+      <c r="AC307" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD307" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE307" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF307" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG307" s="12" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH307" s="12" t="s">
+        <v>1330</v>
+      </c>
+      <c r="AI307" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ307" s="13">
+        <v>45813</v>
+      </c>
+      <c r="AK307" s="13">
+        <v>45813</v>
+      </c>
+      <c r="AL307" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM307" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN307" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO307" s="12">
+        <v>1</v>
+      </c>
+      <c r="AP307" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AQ307" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR307" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS307" s="14">
+        <v>26</v>
+      </c>
+      <c r="AT307" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU307" s="15">
+        <v>26</v>
+      </c>
+      <c r="AV307" s="15">
+        <v>0</v>
+      </c>
+      <c r="AW307" s="12">
+        <v>26</v>
+      </c>
+      <c r="AX307" s="15">
+        <v>26</v>
+      </c>
+      <c r="AY307" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ307" s="12">
+        <v>27</v>
+      </c>
+      <c r="BA307" s="14">
+        <v>27</v>
+      </c>
+      <c r="BB307" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC307" s="16" t="s">
+        <v>1364</v>
+      </c>
+      <c r="BD307" s="13">
+        <v>45852</v>
+      </c>
+      <c r="BE307" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF307" s="12" t="s">
+        <v>1364</v>
+      </c>
+      <c r="BG307" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BH307" s="12" t="s">
+        <v>1364</v>
+      </c>
+      <c r="BI307" s="13">
+        <v>45852</v>
+      </c>
+      <c r="BJ307" s="12">
+        <v>0</v>
+      </c>
+      <c r="BK307" s="12">
+        <v>3</v>
+      </c>
+      <c r="BL307" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="BM307" s="12" t="s">
+        <v>1365</v>
+      </c>
+      <c r="BN307" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BO307" s="12">
+        <v>7</v>
+      </c>
+      <c r="BP307" s="12"/>
+      <c r="BQ307" s="12"/>
+      <c r="BR307" s="12" t="s">
+        <v>1365</v>
+      </c>
+      <c r="BS307" s="13">
+        <v>45861</v>
+      </c>
+      <c r="BT307" s="12" t="s">
+        <v>1328</v>
+      </c>
+      <c r="BU307" s="12">
+        <v>2025</v>
+      </c>
+      <c r="BV307" s="12"/>
+      <c r="BW307" s="12"/>
+      <c r="BX307" s="12">
+        <v>10</v>
+      </c>
+      <c r="BY307" s="14">
+        <v>38</v>
+      </c>
+      <c r="BZ307" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA307" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB307" s="12" t="s">
+        <v>1304</v>
+      </c>
+      <c r="CC307" s="12" t="s">
+        <v>1347</v>
+      </c>
+      <c r="CD307" s="12" t="s">
+        <v>1366</v>
+      </c>
+      <c r="CE307" s="12" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF307" s="17" t="s">
+        <v>1367</v>
+      </c>
+      <c r="CG307" s="18">
+        <v>104054.53</v>
+      </c>
+      <c r="CH307" s="18">
+        <v>3926.59</v>
+      </c>
+      <c r="CI307" s="15" t="s">
+        <v>1310</v>
+      </c>
+      <c r="CJ307" s="12" t="s">
+        <v>1310</v>
+      </c>
+      <c r="CK307" s="15" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="308" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A308" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="B308" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C308" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="D308" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E308" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F308" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="G308" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H308" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I308" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J308" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="K308" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="L308" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M308" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N308" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O308" s="12" t="s">
+        <v>1311</v>
+      </c>
+      <c r="P308" s="13">
+        <v>45821</v>
+      </c>
+      <c r="Q308" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="R308" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S308" s="12" t="s">
+        <v>1463</v>
+      </c>
+      <c r="T308" s="12" t="s">
+        <v>1288</v>
+      </c>
+      <c r="U308" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V308" s="13">
+        <v>45824</v>
+      </c>
+      <c r="W308" s="13">
+        <v>45824</v>
+      </c>
+      <c r="X308" s="12">
+        <v>1</v>
+      </c>
+      <c r="Y308" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z308" s="13">
+        <v>45824</v>
+      </c>
+      <c r="AA308" s="13">
+        <v>45824</v>
+      </c>
+      <c r="AB308" s="12" t="s">
+        <v>1442</v>
+      </c>
+      <c r="AC308" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD308" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE308" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF308" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG308" s="12" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH308" s="12" t="s">
+        <v>1296</v>
+      </c>
+      <c r="AI308" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ308" s="13">
+        <v>45824</v>
+      </c>
+      <c r="AK308" s="13">
+        <v>45824</v>
+      </c>
+      <c r="AL308" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM308" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN308" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO308" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP308" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AQ308" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR308" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS308" s="14" t="s">
+        <v>1299</v>
+      </c>
+      <c r="AT308" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU308" s="15">
+        <v>0</v>
+      </c>
+      <c r="AV308" s="15">
+        <v>0</v>
+      </c>
+      <c r="AW308" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX308" s="15">
+        <v>0</v>
+      </c>
+      <c r="AY308" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ308" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA308" s="14">
+        <v>0</v>
+      </c>
+      <c r="BB308" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC308" s="16" t="s">
+        <v>1377</v>
+      </c>
+      <c r="BD308" s="13">
+        <v>45824</v>
+      </c>
+      <c r="BE308" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF308" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="BG308" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BH308" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="BI308" s="13">
+        <v>45824</v>
+      </c>
+      <c r="BJ308" s="12">
+        <v>0</v>
+      </c>
+      <c r="BK308" s="12">
+        <v>1</v>
+      </c>
+      <c r="BL308" s="15" t="s">
+        <v>1327</v>
+      </c>
+      <c r="BM308" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="BN308" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BO308" s="12">
+        <v>0</v>
+      </c>
+      <c r="BP308" s="12"/>
+      <c r="BQ308" s="12"/>
+      <c r="BR308" s="12"/>
+      <c r="BS308" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BT308" s="12" t="s">
+        <v>1328</v>
+      </c>
+      <c r="BU308" s="12">
+        <v>2026</v>
+      </c>
+      <c r="BV308" s="12"/>
+      <c r="BW308" s="12"/>
+      <c r="BX308" s="12">
+        <v>1</v>
+      </c>
+      <c r="BY308" s="14">
+        <v>1</v>
+      </c>
+      <c r="BZ308" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA308" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB308" s="12" t="s">
+        <v>1441</v>
+      </c>
+      <c r="CC308" s="12" t="s">
+        <v>1319</v>
+      </c>
+      <c r="CD308" s="12" t="s">
+        <v>1349</v>
+      </c>
+      <c r="CE308" s="12" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF308" s="17" t="s">
+        <v>1350</v>
+      </c>
+      <c r="CG308" s="18">
+        <v>1288544.3999999999</v>
+      </c>
+      <c r="CH308" s="18">
+        <v>343.06</v>
+      </c>
+      <c r="CI308" s="15" t="s">
+        <v>1309</v>
+      </c>
+      <c r="CJ308" s="12" t="s">
+        <v>1310</v>
+      </c>
+      <c r="CK308" s="15" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="309" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A309" s="7" t="s">
+        <v>981</v>
+      </c>
+      <c r="B309" s="7" t="s">
+        <v>982</v>
+      </c>
+      <c r="C309" s="7" t="s">
+        <v>983</v>
+      </c>
+      <c r="D309" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="E309" s="9" t="s">
+        <v>786</v>
+      </c>
+      <c r="F309" s="10" t="s">
+        <v>984</v>
+      </c>
+      <c r="G309" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H309" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I309" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J309" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="K309" s="7" t="s">
+        <v>985</v>
+      </c>
+      <c r="L309" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M309" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N309" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O309" s="15" t="s">
+        <v>1285</v>
+      </c>
+      <c r="P309" s="19">
+        <v>45817</v>
+      </c>
+      <c r="Q309" s="15" t="s">
+        <v>1312</v>
+      </c>
+      <c r="R309" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S309" s="15" t="s">
+        <v>1313</v>
+      </c>
+      <c r="T309" s="15" t="s">
+        <v>1314</v>
+      </c>
+      <c r="U309" s="15" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V309" s="19">
+        <v>45818</v>
+      </c>
+      <c r="W309" s="19">
+        <v>45818</v>
+      </c>
+      <c r="X309" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y309" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z309" s="19">
+        <v>45818</v>
+      </c>
+      <c r="AA309" s="19">
+        <v>45818</v>
+      </c>
+      <c r="AB309" s="15" t="s">
+        <v>1405</v>
+      </c>
+      <c r="AC309" s="15" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD309" s="15" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE309" s="15" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF309" s="20">
+        <v>0</v>
+      </c>
+      <c r="AG309" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH309" s="15" t="s">
+        <v>1330</v>
+      </c>
+      <c r="AI309" s="15" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ309" s="19">
+        <v>45819</v>
+      </c>
+      <c r="AK309" s="19">
+        <v>45819</v>
+      </c>
+      <c r="AL309" s="15" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM309" s="15" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN309" s="15" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO309" s="15">
+        <v>1</v>
+      </c>
+      <c r="AP309" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AQ309" s="15" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR309" s="15">
+        <v>0</v>
+      </c>
+      <c r="AS309" s="20">
+        <v>0</v>
+      </c>
+      <c r="AT309" s="15">
+        <v>13</v>
+      </c>
+      <c r="AU309" s="15">
+        <v>0</v>
+      </c>
+      <c r="AV309" s="15">
+        <v>0</v>
+      </c>
+      <c r="AW309" s="15">
+        <v>0</v>
+      </c>
+      <c r="AX309" s="15">
+        <v>0</v>
+      </c>
+      <c r="AY309" s="15">
+        <v>13</v>
+      </c>
+      <c r="AZ309" s="15">
+        <v>14</v>
+      </c>
+      <c r="BA309" s="20">
+        <v>13</v>
+      </c>
+      <c r="BB309" s="15" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC309" s="21" t="s">
+        <v>1409</v>
+      </c>
+      <c r="BD309" s="19">
+        <v>45838</v>
+      </c>
+      <c r="BE309" s="15" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF309" s="15" t="s">
+        <v>1409</v>
+      </c>
+      <c r="BG309" s="19">
+        <v>46219</v>
+      </c>
+      <c r="BH309" s="15" t="s">
+        <v>1403</v>
+      </c>
+      <c r="BI309" s="19">
+        <v>45880</v>
+      </c>
+      <c r="BJ309" s="15">
+        <v>29</v>
+      </c>
+      <c r="BK309" s="15">
+        <v>30</v>
+      </c>
+      <c r="BL309" s="15" t="s">
+        <v>1301</v>
+      </c>
+      <c r="BM309" s="15" t="s">
+        <v>1332</v>
+      </c>
+      <c r="BN309" s="19">
+        <v>46219</v>
+      </c>
+      <c r="BO309" s="15">
+        <v>108</v>
+      </c>
+      <c r="BP309" s="15"/>
+      <c r="BQ309" s="15"/>
+      <c r="BR309" s="15" t="s">
+        <v>1667</v>
+      </c>
+      <c r="BS309" s="19">
+        <v>45952</v>
+      </c>
+      <c r="BT309" s="15" t="s">
+        <v>1433</v>
+      </c>
+      <c r="BU309" s="15">
+        <v>2025</v>
+      </c>
+      <c r="BV309" s="15"/>
+      <c r="BW309" s="15"/>
+      <c r="BX309" s="15">
+        <v>11</v>
+      </c>
+      <c r="BY309" s="20">
+        <v>11</v>
+      </c>
+      <c r="BZ309" s="15" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA309" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB309" s="15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="CC309" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="CD309" s="15" t="s">
+        <v>1349</v>
+      </c>
+      <c r="CE309" s="15" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF309" s="22" t="s">
+        <v>1350</v>
+      </c>
+      <c r="CG309" s="23">
+        <v>787229.2</v>
+      </c>
+    </row>
+    <row r="310" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A310" s="7" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B310" s="7" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C310" s="7" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D310" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="E310" s="7" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F310" s="10" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G310" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H310" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I310" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J310" s="7" t="s">
+        <v>961</v>
+      </c>
+      <c r="K310" s="7"/>
+      <c r="L310" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M310" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N310" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O310" s="12" t="s">
+        <v>1311</v>
+      </c>
+      <c r="P310" s="13">
+        <v>45818</v>
+      </c>
+      <c r="Q310" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="R310" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S310" s="12" t="s">
+        <v>1313</v>
+      </c>
+      <c r="T310" s="12" t="s">
+        <v>1314</v>
+      </c>
+      <c r="U310" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V310" s="13">
+        <v>45818</v>
+      </c>
+      <c r="W310" s="13">
+        <v>45818</v>
+      </c>
+      <c r="X310" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y310" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z310" s="13">
+        <v>45818</v>
+      </c>
+      <c r="AA310" s="13">
+        <v>45818</v>
+      </c>
+      <c r="AB310" s="12" t="s">
+        <v>1405</v>
+      </c>
+      <c r="AC310" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD310" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE310" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF310" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG310" s="12" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH310" s="12" t="s">
+        <v>1336</v>
+      </c>
+      <c r="AI310" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ310" s="13">
+        <v>45821</v>
+      </c>
+      <c r="AK310" s="13">
+        <v>45821</v>
+      </c>
+      <c r="AL310" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM310" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN310" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO310" s="12">
+        <v>3</v>
+      </c>
+      <c r="AP310" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AQ310" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR310" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS310" s="14">
+        <v>0</v>
+      </c>
+      <c r="AT310" s="12">
+        <v>6</v>
+      </c>
+      <c r="AU310" s="15">
+        <v>0</v>
+      </c>
+      <c r="AV310" s="15">
+        <v>-1</v>
+      </c>
+      <c r="AW310" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX310" s="15">
+        <v>0</v>
+      </c>
+      <c r="AY310" s="12">
+        <v>6</v>
+      </c>
+      <c r="AZ310" s="12">
+        <v>9</v>
+      </c>
+      <c r="BA310" s="14">
+        <v>9</v>
+      </c>
+      <c r="BB310" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC310" s="16" t="s">
+        <v>1415</v>
+      </c>
+      <c r="BD310" s="13">
+        <v>45832</v>
+      </c>
+      <c r="BE310" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF310" s="12" t="s">
+        <v>1415</v>
+      </c>
+      <c r="BG310" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BH310" s="12" t="s">
+        <v>1403</v>
+      </c>
+      <c r="BI310" s="13">
+        <v>45880</v>
+      </c>
+      <c r="BJ310" s="12">
+        <v>33</v>
+      </c>
+      <c r="BK310" s="12">
+        <v>33</v>
+      </c>
+      <c r="BL310" s="12" t="s">
+        <v>1327</v>
+      </c>
+      <c r="BM310" s="12"/>
+      <c r="BN310" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BO310" s="15">
+        <v>117</v>
+      </c>
+      <c r="BP310" s="15"/>
+      <c r="BQ310" s="15"/>
+      <c r="BR310" s="15" t="s">
+        <v>1685</v>
+      </c>
+      <c r="BS310" s="19">
+        <v>45961</v>
+      </c>
+      <c r="BT310" s="15" t="s">
+        <v>1303</v>
+      </c>
+      <c r="BU310" s="15">
+        <v>2025</v>
+      </c>
+      <c r="BV310" s="15"/>
+      <c r="BW310" s="15"/>
+      <c r="BX310" s="15">
+        <v>11</v>
+      </c>
+      <c r="BY310" s="20">
+        <v>11</v>
+      </c>
+      <c r="BZ310" s="15" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA310" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB310" s="15" t="s">
+        <v>1686</v>
+      </c>
+      <c r="CC310" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="CD310" s="15" t="s">
+        <v>1349</v>
+      </c>
+      <c r="CE310" s="15" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF310" s="22" t="s">
+        <v>1350</v>
+      </c>
+      <c r="CG310" s="23">
+        <v>787238.2</v>
+      </c>
+    </row>
+    <row r="311" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A311" s="7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B311" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C311" s="7" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D311" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E311" s="7" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F311" s="10" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G311" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H311" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I311" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J311" s="7" t="s">
+        <v>1155</v>
+      </c>
+      <c r="K311" s="7"/>
+      <c r="L311" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M311" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N311" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O311" s="12" t="s">
+        <v>1311</v>
+      </c>
+      <c r="P311" s="13">
+        <v>45789</v>
+      </c>
+      <c r="Q311" s="12" t="s">
+        <v>1286</v>
+      </c>
+      <c r="R311" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S311" s="12" t="s">
+        <v>1287</v>
+      </c>
+      <c r="T311" s="12" t="s">
+        <v>1314</v>
+      </c>
+      <c r="U311" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V311" s="13">
+        <v>45812</v>
+      </c>
+      <c r="W311" s="13">
+        <v>45812</v>
+      </c>
+      <c r="X311" s="12">
+        <v>17</v>
+      </c>
+      <c r="Y311" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z311" s="13">
+        <v>45812</v>
+      </c>
+      <c r="AA311" s="13">
+        <v>45812</v>
+      </c>
+      <c r="AB311" s="12" t="s">
+        <v>1355</v>
+      </c>
+      <c r="AC311" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD311" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE311" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF311" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG311" s="12" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH311" s="12" t="s">
+        <v>1339</v>
+      </c>
+      <c r="AI311" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ311" s="13">
+        <v>45821</v>
+      </c>
+      <c r="AK311" s="13">
+        <v>45821</v>
+      </c>
+      <c r="AL311" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM311" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN311" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO311" s="12">
+        <v>7</v>
+      </c>
+      <c r="AP311" s="15" t="s">
+        <v>1370</v>
+      </c>
+      <c r="AQ311" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR311" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS311" s="14">
+        <v>0</v>
+      </c>
+      <c r="AT311" s="12">
+        <v>19</v>
+      </c>
+      <c r="AU311" s="15">
+        <v>0</v>
+      </c>
+      <c r="AV311" s="15">
+        <v>0</v>
+      </c>
+      <c r="AW311" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX311" s="15">
+        <v>0</v>
+      </c>
+      <c r="AY311" s="12">
+        <v>19</v>
+      </c>
+      <c r="AZ311" s="12">
+        <v>26</v>
+      </c>
+      <c r="BA311" s="14">
+        <v>26</v>
+      </c>
+      <c r="BB311" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC311" s="16" t="s">
+        <v>1371</v>
+      </c>
+      <c r="BD311" s="13">
+        <v>45849</v>
+      </c>
+      <c r="BE311" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF311" s="12" t="s">
+        <v>1371</v>
+      </c>
+      <c r="BG311" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BH311" s="12" t="s">
+        <v>1364</v>
+      </c>
+      <c r="BI311" s="13">
+        <v>45852</v>
+      </c>
+      <c r="BJ311" s="12">
+        <v>1</v>
+      </c>
+      <c r="BK311" s="12">
+        <v>18</v>
+      </c>
+      <c r="BL311" s="12" t="s">
+        <v>1327</v>
+      </c>
+      <c r="BM311" s="12"/>
+      <c r="BN311" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BO311" s="15">
+        <v>145</v>
+      </c>
+      <c r="BP311" s="15"/>
+      <c r="BQ311" s="15"/>
+      <c r="BR311" s="15" t="s">
+        <v>1741</v>
+      </c>
+      <c r="BS311" s="19">
+        <v>45989</v>
+      </c>
+      <c r="BT311" s="15" t="s">
+        <v>1454</v>
+      </c>
+      <c r="BU311" s="15">
+        <v>2025</v>
+      </c>
+      <c r="BV311" s="15"/>
+      <c r="BW311" s="15"/>
+      <c r="BX311" s="15">
+        <v>11</v>
+      </c>
+      <c r="BY311" s="20">
+        <v>11</v>
+      </c>
+      <c r="BZ311" s="15" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA311" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB311" s="15" t="s">
+        <v>1742</v>
+      </c>
+      <c r="CC311" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="CD311" s="15" t="s">
+        <v>1349</v>
+      </c>
+      <c r="CE311" s="15" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF311" s="22" t="s">
+        <v>1350</v>
+      </c>
+      <c r="CG311" s="23">
+        <v>787266.2</v>
+      </c>
+    </row>
+    <row r="312" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A312" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C312" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E312" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F312" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G312" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H312" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I312" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J312" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K312" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="L312" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M312" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N312" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O312" s="12" t="s">
+        <v>1285</v>
+      </c>
+      <c r="P312" s="13">
+        <v>45807</v>
+      </c>
+      <c r="Q312" s="12" t="s">
+        <v>1286</v>
+      </c>
+      <c r="R312" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S312" s="12" t="s">
+        <v>1287</v>
+      </c>
+      <c r="T312" s="12" t="s">
+        <v>1314</v>
+      </c>
+      <c r="U312" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V312" s="13">
+        <v>45812</v>
+      </c>
+      <c r="W312" s="13">
+        <v>45812</v>
+      </c>
+      <c r="X312" s="12">
+        <v>3</v>
+      </c>
+      <c r="Y312" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z312" s="13">
+        <v>45812</v>
+      </c>
+      <c r="AA312" s="13">
+        <v>45812</v>
+      </c>
+      <c r="AB312" s="12" t="s">
+        <v>1355</v>
+      </c>
+      <c r="AC312" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD312" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE312" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF312" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG312" s="12" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH312" s="12" t="s">
+        <v>1330</v>
+      </c>
+      <c r="AI312" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ312" s="13">
+        <v>45813</v>
+      </c>
+      <c r="AK312" s="13">
+        <v>45813</v>
+      </c>
+      <c r="AL312" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM312" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN312" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO312" s="12">
+        <v>1</v>
+      </c>
+      <c r="AP312" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AQ312" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR312" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS312" s="14">
+        <v>26</v>
+      </c>
+      <c r="AT312" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU312" s="15">
+        <v>26</v>
+      </c>
+      <c r="AV312" s="15">
+        <v>0</v>
+      </c>
+      <c r="AW312" s="12">
+        <v>26</v>
+      </c>
+      <c r="AX312" s="15">
+        <v>26</v>
+      </c>
+      <c r="AY312" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ312" s="12">
+        <v>27</v>
+      </c>
+      <c r="BA312" s="14">
+        <v>27</v>
+      </c>
+      <c r="BB312" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC312" s="16" t="s">
+        <v>1364</v>
+      </c>
+      <c r="BD312" s="13">
+        <v>45852</v>
+      </c>
+      <c r="BE312" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF312" s="12" t="s">
+        <v>1364</v>
+      </c>
+      <c r="BG312" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BH312" s="12" t="s">
+        <v>1364</v>
+      </c>
+      <c r="BI312" s="13">
+        <v>45852</v>
+      </c>
+      <c r="BJ312" s="12">
+        <v>0</v>
+      </c>
+      <c r="BK312" s="12">
+        <v>3</v>
+      </c>
+      <c r="BL312" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="BM312" s="12" t="s">
+        <v>1365</v>
+      </c>
+      <c r="BN312" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BO312" s="12">
+        <v>7</v>
+      </c>
+      <c r="BP312" s="12"/>
+      <c r="BQ312" s="12"/>
+      <c r="BR312" s="12" t="s">
+        <v>1365</v>
+      </c>
+      <c r="BS312" s="13">
+        <v>45861</v>
+      </c>
+      <c r="BT312" s="12" t="s">
+        <v>1328</v>
+      </c>
+      <c r="BU312" s="12">
+        <v>2025</v>
+      </c>
+      <c r="BV312" s="12"/>
+      <c r="BW312" s="12"/>
+      <c r="BX312" s="12">
+        <v>10</v>
+      </c>
+      <c r="BY312" s="14">
+        <v>38</v>
+      </c>
+      <c r="BZ312" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA312" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB312" s="12" t="s">
+        <v>1304</v>
+      </c>
+      <c r="CC312" s="12" t="s">
+        <v>1347</v>
+      </c>
+      <c r="CD312" s="12" t="s">
+        <v>1366</v>
+      </c>
+      <c r="CE312" s="12" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF312" s="17" t="s">
+        <v>1367</v>
+      </c>
+      <c r="CG312" s="18">
+        <v>104054.53</v>
+      </c>
+      <c r="CH312" s="18">
+        <v>3926.59</v>
+      </c>
+      <c r="CI312" s="15" t="s">
+        <v>1310</v>
+      </c>
+      <c r="CJ312" s="12" t="s">
+        <v>1310</v>
+      </c>
+      <c r="CK312" s="15" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="313" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A313" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="B313" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C313" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="D313" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E313" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F313" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="G313" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H313" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I313" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J313" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="K313" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="L313" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M313" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N313" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O313" s="12" t="s">
+        <v>1311</v>
+      </c>
+      <c r="P313" s="13">
+        <v>45821</v>
+      </c>
+      <c r="Q313" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="R313" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S313" s="12" t="s">
+        <v>1463</v>
+      </c>
+      <c r="T313" s="12" t="s">
+        <v>1288</v>
+      </c>
+      <c r="U313" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V313" s="13">
+        <v>45824</v>
+      </c>
+      <c r="W313" s="13">
+        <v>45824</v>
+      </c>
+      <c r="X313" s="12">
+        <v>1</v>
+      </c>
+      <c r="Y313" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z313" s="13">
+        <v>45824</v>
+      </c>
+      <c r="AA313" s="13">
+        <v>45824</v>
+      </c>
+      <c r="AB313" s="12" t="s">
+        <v>1442</v>
+      </c>
+      <c r="AC313" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD313" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE313" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF313" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG313" s="12" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH313" s="12" t="s">
+        <v>1296</v>
+      </c>
+      <c r="AI313" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ313" s="13">
+        <v>45824</v>
+      </c>
+      <c r="AK313" s="13">
+        <v>45824</v>
+      </c>
+      <c r="AL313" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM313" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN313" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO313" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP313" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AQ313" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR313" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS313" s="14" t="s">
+        <v>1299</v>
+      </c>
+      <c r="AT313" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU313" s="15">
+        <v>0</v>
+      </c>
+      <c r="AV313" s="15">
+        <v>0</v>
+      </c>
+      <c r="AW313" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX313" s="15">
+        <v>0</v>
+      </c>
+      <c r="AY313" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ313" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA313" s="14">
+        <v>0</v>
+      </c>
+      <c r="BB313" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC313" s="16" t="s">
+        <v>1377</v>
+      </c>
+      <c r="BD313" s="13">
+        <v>45824</v>
+      </c>
+      <c r="BE313" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF313" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="BG313" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BH313" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="BI313" s="13">
+        <v>45824</v>
+      </c>
+      <c r="BJ313" s="12">
+        <v>0</v>
+      </c>
+      <c r="BK313" s="12">
+        <v>1</v>
+      </c>
+      <c r="BL313" s="15" t="s">
+        <v>1327</v>
+      </c>
+      <c r="BM313" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="BN313" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BO313" s="12">
+        <v>0</v>
+      </c>
+      <c r="BP313" s="12"/>
+      <c r="BQ313" s="12"/>
+      <c r="BR313" s="12"/>
+      <c r="BS313" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BT313" s="12" t="s">
+        <v>1328</v>
+      </c>
+      <c r="BU313" s="12">
+        <v>2026</v>
+      </c>
+      <c r="BV313" s="12"/>
+      <c r="BW313" s="12"/>
+      <c r="BX313" s="12">
+        <v>1</v>
+      </c>
+      <c r="BY313" s="14">
+        <v>1</v>
+      </c>
+      <c r="BZ313" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA313" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB313" s="12" t="s">
+        <v>1441</v>
+      </c>
+      <c r="CC313" s="12" t="s">
+        <v>1319</v>
+      </c>
+      <c r="CD313" s="12" t="s">
+        <v>1349</v>
+      </c>
+      <c r="CE313" s="12" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF313" s="17" t="s">
+        <v>1350</v>
+      </c>
+      <c r="CG313" s="18">
+        <v>1288544.3999999999</v>
+      </c>
+      <c r="CH313" s="18">
+        <v>343.06</v>
+      </c>
+      <c r="CI313" s="15" t="s">
+        <v>1309</v>
+      </c>
+      <c r="CJ313" s="12" t="s">
+        <v>1310</v>
+      </c>
+      <c r="CK313" s="15" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="314" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A314" s="7" t="s">
+        <v>981</v>
+      </c>
+      <c r="B314" s="7" t="s">
+        <v>982</v>
+      </c>
+      <c r="C314" s="7" t="s">
+        <v>983</v>
+      </c>
+      <c r="D314" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="E314" s="9" t="s">
+        <v>786</v>
+      </c>
+      <c r="F314" s="10" t="s">
+        <v>984</v>
+      </c>
+      <c r="G314" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H314" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I314" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J314" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="K314" s="7" t="s">
+        <v>985</v>
+      </c>
+      <c r="L314" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M314" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N314" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O314" s="15" t="s">
+        <v>1285</v>
+      </c>
+      <c r="P314" s="19">
+        <v>45817</v>
+      </c>
+      <c r="Q314" s="15" t="s">
+        <v>1312</v>
+      </c>
+      <c r="R314" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S314" s="15" t="s">
+        <v>1313</v>
+      </c>
+      <c r="T314" s="15" t="s">
+        <v>1314</v>
+      </c>
+      <c r="U314" s="15" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V314" s="19">
+        <v>45818</v>
+      </c>
+      <c r="W314" s="19">
+        <v>45818</v>
+      </c>
+      <c r="X314" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y314" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z314" s="19">
+        <v>45818</v>
+      </c>
+      <c r="AA314" s="19">
+        <v>45818</v>
+      </c>
+      <c r="AB314" s="15" t="s">
+        <v>1405</v>
+      </c>
+      <c r="AC314" s="15" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD314" s="15" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE314" s="15" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF314" s="20">
+        <v>0</v>
+      </c>
+      <c r="AG314" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH314" s="15" t="s">
+        <v>1330</v>
+      </c>
+      <c r="AI314" s="15" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ314" s="19">
+        <v>45819</v>
+      </c>
+      <c r="AK314" s="19">
+        <v>45819</v>
+      </c>
+      <c r="AL314" s="15" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM314" s="15" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN314" s="15" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO314" s="15">
+        <v>1</v>
+      </c>
+      <c r="AP314" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AQ314" s="15" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR314" s="15">
+        <v>0</v>
+      </c>
+      <c r="AS314" s="20">
+        <v>0</v>
+      </c>
+      <c r="AT314" s="15">
+        <v>13</v>
+      </c>
+      <c r="AU314" s="15">
+        <v>0</v>
+      </c>
+      <c r="AV314" s="15">
+        <v>0</v>
+      </c>
+      <c r="AW314" s="15">
+        <v>0</v>
+      </c>
+      <c r="AX314" s="15">
+        <v>0</v>
+      </c>
+      <c r="AY314" s="15">
+        <v>13</v>
+      </c>
+      <c r="AZ314" s="15">
+        <v>14</v>
+      </c>
+      <c r="BA314" s="20">
+        <v>13</v>
+      </c>
+      <c r="BB314" s="15" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC314" s="21" t="s">
+        <v>1409</v>
+      </c>
+      <c r="BD314" s="19">
+        <v>45838</v>
+      </c>
+      <c r="BE314" s="15" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF314" s="15" t="s">
+        <v>1409</v>
+      </c>
+      <c r="BG314" s="19">
+        <v>46219</v>
+      </c>
+      <c r="BH314" s="15" t="s">
+        <v>1403</v>
+      </c>
+      <c r="BI314" s="19">
+        <v>45880</v>
+      </c>
+      <c r="BJ314" s="15">
+        <v>29</v>
+      </c>
+      <c r="BK314" s="15">
+        <v>30</v>
+      </c>
+      <c r="BL314" s="15" t="s">
+        <v>1301</v>
+      </c>
+      <c r="BM314" s="15" t="s">
+        <v>1332</v>
+      </c>
+      <c r="BN314" s="19">
+        <v>46219</v>
+      </c>
+      <c r="BO314" s="15">
+        <v>108</v>
+      </c>
+      <c r="BP314" s="15"/>
+      <c r="BQ314" s="15"/>
+      <c r="BR314" s="15" t="s">
+        <v>1667</v>
+      </c>
+      <c r="BS314" s="19">
+        <v>45952</v>
+      </c>
+      <c r="BT314" s="15" t="s">
+        <v>1433</v>
+      </c>
+      <c r="BU314" s="15">
+        <v>2025</v>
+      </c>
+      <c r="BV314" s="15"/>
+      <c r="BW314" s="15"/>
+      <c r="BX314" s="15">
+        <v>11</v>
+      </c>
+      <c r="BY314" s="20">
+        <v>11</v>
+      </c>
+      <c r="BZ314" s="15" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA314" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB314" s="15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="CC314" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="CD314" s="15" t="s">
+        <v>1349</v>
+      </c>
+      <c r="CE314" s="15" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF314" s="22" t="s">
+        <v>1350</v>
+      </c>
+      <c r="CG314" s="23">
+        <v>787229.2</v>
+      </c>
+    </row>
+    <row r="315" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A315" s="7" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B315" s="7" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C315" s="7" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D315" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="E315" s="7" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F315" s="10" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G315" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H315" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I315" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J315" s="7" t="s">
+        <v>961</v>
+      </c>
+      <c r="K315" s="7"/>
+      <c r="L315" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M315" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N315" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O315" s="12" t="s">
+        <v>1311</v>
+      </c>
+      <c r="P315" s="13">
+        <v>45818</v>
+      </c>
+      <c r="Q315" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="R315" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S315" s="12" t="s">
+        <v>1313</v>
+      </c>
+      <c r="T315" s="12" t="s">
+        <v>1314</v>
+      </c>
+      <c r="U315" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V315" s="13">
+        <v>45818</v>
+      </c>
+      <c r="W315" s="13">
+        <v>45818</v>
+      </c>
+      <c r="X315" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y315" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z315" s="13">
+        <v>45818</v>
+      </c>
+      <c r="AA315" s="13">
+        <v>45818</v>
+      </c>
+      <c r="AB315" s="12" t="s">
+        <v>1405</v>
+      </c>
+      <c r="AC315" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD315" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE315" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF315" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG315" s="12" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH315" s="12" t="s">
+        <v>1336</v>
+      </c>
+      <c r="AI315" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ315" s="13">
+        <v>45821</v>
+      </c>
+      <c r="AK315" s="13">
+        <v>45821</v>
+      </c>
+      <c r="AL315" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM315" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN315" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO315" s="12">
+        <v>3</v>
+      </c>
+      <c r="AP315" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AQ315" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR315" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS315" s="14">
+        <v>0</v>
+      </c>
+      <c r="AT315" s="12">
+        <v>6</v>
+      </c>
+      <c r="AU315" s="15">
+        <v>0</v>
+      </c>
+      <c r="AV315" s="15">
+        <v>-1</v>
+      </c>
+      <c r="AW315" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX315" s="15">
+        <v>0</v>
+      </c>
+      <c r="AY315" s="12">
+        <v>6</v>
+      </c>
+      <c r="AZ315" s="12">
+        <v>9</v>
+      </c>
+      <c r="BA315" s="14">
+        <v>9</v>
+      </c>
+      <c r="BB315" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC315" s="16" t="s">
+        <v>1415</v>
+      </c>
+      <c r="BD315" s="13">
+        <v>45832</v>
+      </c>
+      <c r="BE315" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF315" s="12" t="s">
+        <v>1415</v>
+      </c>
+      <c r="BG315" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BH315" s="12" t="s">
+        <v>1403</v>
+      </c>
+      <c r="BI315" s="13">
+        <v>45880</v>
+      </c>
+      <c r="BJ315" s="12">
+        <v>33</v>
+      </c>
+      <c r="BK315" s="12">
+        <v>33</v>
+      </c>
+      <c r="BL315" s="12" t="s">
+        <v>1327</v>
+      </c>
+      <c r="BM315" s="12"/>
+      <c r="BN315" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BO315" s="15">
+        <v>117</v>
+      </c>
+      <c r="BP315" s="15"/>
+      <c r="BQ315" s="15"/>
+      <c r="BR315" s="15" t="s">
+        <v>1685</v>
+      </c>
+      <c r="BS315" s="19">
+        <v>45961</v>
+      </c>
+      <c r="BT315" s="15" t="s">
+        <v>1303</v>
+      </c>
+      <c r="BU315" s="15">
+        <v>2025</v>
+      </c>
+      <c r="BV315" s="15"/>
+      <c r="BW315" s="15"/>
+      <c r="BX315" s="15">
+        <v>11</v>
+      </c>
+      <c r="BY315" s="20">
+        <v>11</v>
+      </c>
+      <c r="BZ315" s="15" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA315" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB315" s="15" t="s">
+        <v>1686</v>
+      </c>
+      <c r="CC315" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="CD315" s="15" t="s">
+        <v>1349</v>
+      </c>
+      <c r="CE315" s="15" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF315" s="22" t="s">
+        <v>1350</v>
+      </c>
+      <c r="CG315" s="23">
+        <v>787238.2</v>
+      </c>
+    </row>
+    <row r="316" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A316" s="7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B316" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C316" s="7" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D316" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E316" s="7" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F316" s="10" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G316" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H316" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I316" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J316" s="7" t="s">
+        <v>1155</v>
+      </c>
+      <c r="K316" s="7"/>
+      <c r="L316" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M316" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N316" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O316" s="12" t="s">
+        <v>1311</v>
+      </c>
+      <c r="P316" s="13">
+        <v>45789</v>
+      </c>
+      <c r="Q316" s="12" t="s">
+        <v>1286</v>
+      </c>
+      <c r="R316" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S316" s="12" t="s">
+        <v>1287</v>
+      </c>
+      <c r="T316" s="12" t="s">
+        <v>1314</v>
+      </c>
+      <c r="U316" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V316" s="13">
+        <v>45812</v>
+      </c>
+      <c r="W316" s="13">
+        <v>45812</v>
+      </c>
+      <c r="X316" s="12">
+        <v>17</v>
+      </c>
+      <c r="Y316" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z316" s="13">
+        <v>45812</v>
+      </c>
+      <c r="AA316" s="13">
+        <v>45812</v>
+      </c>
+      <c r="AB316" s="12" t="s">
+        <v>1355</v>
+      </c>
+      <c r="AC316" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD316" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE316" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF316" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG316" s="12" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH316" s="12" t="s">
+        <v>1339</v>
+      </c>
+      <c r="AI316" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ316" s="13">
+        <v>45821</v>
+      </c>
+      <c r="AK316" s="13">
+        <v>45821</v>
+      </c>
+      <c r="AL316" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM316" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN316" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO316" s="12">
+        <v>7</v>
+      </c>
+      <c r="AP316" s="15" t="s">
+        <v>1370</v>
+      </c>
+      <c r="AQ316" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR316" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS316" s="14">
+        <v>0</v>
+      </c>
+      <c r="AT316" s="12">
+        <v>19</v>
+      </c>
+      <c r="AU316" s="15">
+        <v>0</v>
+      </c>
+      <c r="AV316" s="15">
+        <v>0</v>
+      </c>
+      <c r="AW316" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX316" s="15">
+        <v>0</v>
+      </c>
+      <c r="AY316" s="12">
+        <v>19</v>
+      </c>
+      <c r="AZ316" s="12">
+        <v>26</v>
+      </c>
+      <c r="BA316" s="14">
+        <v>26</v>
+      </c>
+      <c r="BB316" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC316" s="16" t="s">
+        <v>1371</v>
+      </c>
+      <c r="BD316" s="13">
+        <v>45849</v>
+      </c>
+      <c r="BE316" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF316" s="12" t="s">
+        <v>1371</v>
+      </c>
+      <c r="BG316" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BH316" s="12" t="s">
+        <v>1364</v>
+      </c>
+      <c r="BI316" s="13">
+        <v>45852</v>
+      </c>
+      <c r="BJ316" s="12">
+        <v>1</v>
+      </c>
+      <c r="BK316" s="12">
+        <v>18</v>
+      </c>
+      <c r="BL316" s="12" t="s">
+        <v>1327</v>
+      </c>
+      <c r="BM316" s="12"/>
+      <c r="BN316" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BO316" s="15">
+        <v>145</v>
+      </c>
+      <c r="BP316" s="15"/>
+      <c r="BQ316" s="15"/>
+      <c r="BR316" s="15" t="s">
+        <v>1741</v>
+      </c>
+      <c r="BS316" s="19">
+        <v>45989</v>
+      </c>
+      <c r="BT316" s="15" t="s">
+        <v>1454</v>
+      </c>
+      <c r="BU316" s="15">
+        <v>2025</v>
+      </c>
+      <c r="BV316" s="15"/>
+      <c r="BW316" s="15"/>
+      <c r="BX316" s="15">
+        <v>11</v>
+      </c>
+      <c r="BY316" s="20">
+        <v>11</v>
+      </c>
+      <c r="BZ316" s="15" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA316" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB316" s="15" t="s">
+        <v>1742</v>
+      </c>
+      <c r="CC316" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="CD316" s="15" t="s">
+        <v>1349</v>
+      </c>
+      <c r="CE316" s="15" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF316" s="22" t="s">
+        <v>1350</v>
+      </c>
+      <c r="CG316" s="23">
+        <v>787266.2</v>
+      </c>
+    </row>
+    <row r="317" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A317" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C317" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D317" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E317" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F317" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G317" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H317" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I317" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J317" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K317" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="L317" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M317" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N317" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O317" s="12" t="s">
+        <v>1285</v>
+      </c>
+      <c r="P317" s="13">
+        <v>45807</v>
+      </c>
+      <c r="Q317" s="12" t="s">
+        <v>1286</v>
+      </c>
+      <c r="R317" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S317" s="12" t="s">
+        <v>1287</v>
+      </c>
+      <c r="T317" s="12" t="s">
+        <v>1314</v>
+      </c>
+      <c r="U317" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V317" s="13">
+        <v>45812</v>
+      </c>
+      <c r="W317" s="13">
+        <v>45812</v>
+      </c>
+      <c r="X317" s="12">
+        <v>3</v>
+      </c>
+      <c r="Y317" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z317" s="13">
+        <v>45812</v>
+      </c>
+      <c r="AA317" s="13">
+        <v>45812</v>
+      </c>
+      <c r="AB317" s="12" t="s">
+        <v>1355</v>
+      </c>
+      <c r="AC317" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD317" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE317" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF317" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG317" s="12" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH317" s="12" t="s">
+        <v>1330</v>
+      </c>
+      <c r="AI317" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ317" s="13">
+        <v>45813</v>
+      </c>
+      <c r="AK317" s="13">
+        <v>45813</v>
+      </c>
+      <c r="AL317" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM317" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN317" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO317" s="12">
+        <v>1</v>
+      </c>
+      <c r="AP317" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AQ317" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR317" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS317" s="14">
+        <v>26</v>
+      </c>
+      <c r="AT317" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU317" s="15">
+        <v>26</v>
+      </c>
+      <c r="AV317" s="15">
+        <v>0</v>
+      </c>
+      <c r="AW317" s="12">
+        <v>26</v>
+      </c>
+      <c r="AX317" s="15">
+        <v>26</v>
+      </c>
+      <c r="AY317" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ317" s="12">
+        <v>27</v>
+      </c>
+      <c r="BA317" s="14">
+        <v>27</v>
+      </c>
+      <c r="BB317" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC317" s="16" t="s">
+        <v>1364</v>
+      </c>
+      <c r="BD317" s="13">
+        <v>45852</v>
+      </c>
+      <c r="BE317" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF317" s="12" t="s">
+        <v>1364</v>
+      </c>
+      <c r="BG317" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BH317" s="12" t="s">
+        <v>1364</v>
+      </c>
+      <c r="BI317" s="13">
+        <v>45852</v>
+      </c>
+      <c r="BJ317" s="12">
+        <v>0</v>
+      </c>
+      <c r="BK317" s="12">
+        <v>3</v>
+      </c>
+      <c r="BL317" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="BM317" s="12" t="s">
+        <v>1365</v>
+      </c>
+      <c r="BN317" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BO317" s="12">
+        <v>7</v>
+      </c>
+      <c r="BP317" s="12"/>
+      <c r="BQ317" s="12"/>
+      <c r="BR317" s="12" t="s">
+        <v>1365</v>
+      </c>
+      <c r="BS317" s="13">
+        <v>45861</v>
+      </c>
+      <c r="BT317" s="12" t="s">
+        <v>1328</v>
+      </c>
+      <c r="BU317" s="12">
+        <v>2025</v>
+      </c>
+      <c r="BV317" s="12"/>
+      <c r="BW317" s="12"/>
+      <c r="BX317" s="12">
+        <v>10</v>
+      </c>
+      <c r="BY317" s="14">
+        <v>38</v>
+      </c>
+      <c r="BZ317" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA317" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB317" s="12" t="s">
+        <v>1304</v>
+      </c>
+      <c r="CC317" s="12" t="s">
+        <v>1347</v>
+      </c>
+      <c r="CD317" s="12" t="s">
+        <v>1366</v>
+      </c>
+      <c r="CE317" s="12" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF317" s="17" t="s">
+        <v>1367</v>
+      </c>
+      <c r="CG317" s="18">
+        <v>104054.53</v>
+      </c>
+      <c r="CH317" s="18">
+        <v>3926.59</v>
+      </c>
+      <c r="CI317" s="15" t="s">
+        <v>1310</v>
+      </c>
+      <c r="CJ317" s="12" t="s">
+        <v>1310</v>
+      </c>
+      <c r="CK317" s="15" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="318" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A318" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="B318" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C318" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="D318" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E318" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F318" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="G318" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H318" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I318" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J318" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="K318" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="L318" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M318" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N318" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O318" s="12" t="s">
+        <v>1311</v>
+      </c>
+      <c r="P318" s="13">
+        <v>45821</v>
+      </c>
+      <c r="Q318" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="R318" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S318" s="12" t="s">
+        <v>1463</v>
+      </c>
+      <c r="T318" s="12" t="s">
+        <v>1288</v>
+      </c>
+      <c r="U318" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V318" s="13">
+        <v>45824</v>
+      </c>
+      <c r="W318" s="13">
+        <v>45824</v>
+      </c>
+      <c r="X318" s="12">
+        <v>1</v>
+      </c>
+      <c r="Y318" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z318" s="13">
+        <v>45824</v>
+      </c>
+      <c r="AA318" s="13">
+        <v>45824</v>
+      </c>
+      <c r="AB318" s="12" t="s">
+        <v>1442</v>
+      </c>
+      <c r="AC318" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD318" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE318" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF318" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG318" s="12" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH318" s="12" t="s">
+        <v>1296</v>
+      </c>
+      <c r="AI318" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ318" s="13">
+        <v>45824</v>
+      </c>
+      <c r="AK318" s="13">
+        <v>45824</v>
+      </c>
+      <c r="AL318" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM318" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN318" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO318" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP318" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AQ318" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR318" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS318" s="14" t="s">
+        <v>1299</v>
+      </c>
+      <c r="AT318" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU318" s="15">
+        <v>0</v>
+      </c>
+      <c r="AV318" s="15">
+        <v>0</v>
+      </c>
+      <c r="AW318" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX318" s="15">
+        <v>0</v>
+      </c>
+      <c r="AY318" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ318" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA318" s="14">
+        <v>0</v>
+      </c>
+      <c r="BB318" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC318" s="16" t="s">
+        <v>1377</v>
+      </c>
+      <c r="BD318" s="13">
+        <v>45824</v>
+      </c>
+      <c r="BE318" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF318" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="BG318" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BH318" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="BI318" s="13">
+        <v>45824</v>
+      </c>
+      <c r="BJ318" s="12">
+        <v>0</v>
+      </c>
+      <c r="BK318" s="12">
+        <v>1</v>
+      </c>
+      <c r="BL318" s="15" t="s">
+        <v>1327</v>
+      </c>
+      <c r="BM318" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="BN318" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BO318" s="12">
+        <v>0</v>
+      </c>
+      <c r="BP318" s="12"/>
+      <c r="BQ318" s="12"/>
+      <c r="BR318" s="12"/>
+      <c r="BS318" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BT318" s="12" t="s">
+        <v>1328</v>
+      </c>
+      <c r="BU318" s="12">
+        <v>2026</v>
+      </c>
+      <c r="BV318" s="12"/>
+      <c r="BW318" s="12"/>
+      <c r="BX318" s="12">
+        <v>1</v>
+      </c>
+      <c r="BY318" s="14">
+        <v>1</v>
+      </c>
+      <c r="BZ318" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA318" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB318" s="12" t="s">
+        <v>1441</v>
+      </c>
+      <c r="CC318" s="12" t="s">
+        <v>1319</v>
+      </c>
+      <c r="CD318" s="12" t="s">
+        <v>1349</v>
+      </c>
+      <c r="CE318" s="12" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF318" s="17" t="s">
+        <v>1350</v>
+      </c>
+      <c r="CG318" s="18">
+        <v>1288544.3999999999</v>
+      </c>
+      <c r="CH318" s="18">
+        <v>343.06</v>
+      </c>
+      <c r="CI318" s="15" t="s">
+        <v>1309</v>
+      </c>
+      <c r="CJ318" s="12" t="s">
+        <v>1310</v>
+      </c>
+      <c r="CK318" s="15" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="319" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A319" s="7" t="s">
+        <v>981</v>
+      </c>
+      <c r="B319" s="7" t="s">
+        <v>982</v>
+      </c>
+      <c r="C319" s="7" t="s">
+        <v>983</v>
+      </c>
+      <c r="D319" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="E319" s="9" t="s">
+        <v>786</v>
+      </c>
+      <c r="F319" s="10" t="s">
+        <v>984</v>
+      </c>
+      <c r="G319" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H319" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I319" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J319" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="K319" s="7" t="s">
+        <v>985</v>
+      </c>
+      <c r="L319" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M319" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N319" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O319" s="15" t="s">
+        <v>1285</v>
+      </c>
+      <c r="P319" s="19">
+        <v>45817</v>
+      </c>
+      <c r="Q319" s="15" t="s">
+        <v>1312</v>
+      </c>
+      <c r="R319" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S319" s="15" t="s">
+        <v>1313</v>
+      </c>
+      <c r="T319" s="15" t="s">
+        <v>1314</v>
+      </c>
+      <c r="U319" s="15" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V319" s="19">
+        <v>45818</v>
+      </c>
+      <c r="W319" s="19">
+        <v>45818</v>
+      </c>
+      <c r="X319" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y319" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z319" s="19">
+        <v>45818</v>
+      </c>
+      <c r="AA319" s="19">
+        <v>45818</v>
+      </c>
+      <c r="AB319" s="15" t="s">
+        <v>1405</v>
+      </c>
+      <c r="AC319" s="15" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD319" s="15" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE319" s="15" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF319" s="20">
+        <v>0</v>
+      </c>
+      <c r="AG319" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH319" s="15" t="s">
+        <v>1330</v>
+      </c>
+      <c r="AI319" s="15" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ319" s="19">
+        <v>45819</v>
+      </c>
+      <c r="AK319" s="19">
+        <v>45819</v>
+      </c>
+      <c r="AL319" s="15" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM319" s="15" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN319" s="15" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO319" s="15">
+        <v>1</v>
+      </c>
+      <c r="AP319" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AQ319" s="15" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR319" s="15">
+        <v>0</v>
+      </c>
+      <c r="AS319" s="20">
+        <v>0</v>
+      </c>
+      <c r="AT319" s="15">
+        <v>13</v>
+      </c>
+      <c r="AU319" s="15">
+        <v>0</v>
+      </c>
+      <c r="AV319" s="15">
+        <v>0</v>
+      </c>
+      <c r="AW319" s="15">
+        <v>0</v>
+      </c>
+      <c r="AX319" s="15">
+        <v>0</v>
+      </c>
+      <c r="AY319" s="15">
+        <v>13</v>
+      </c>
+      <c r="AZ319" s="15">
+        <v>14</v>
+      </c>
+      <c r="BA319" s="20">
+        <v>13</v>
+      </c>
+      <c r="BB319" s="15" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC319" s="21" t="s">
+        <v>1409</v>
+      </c>
+      <c r="BD319" s="19">
+        <v>45838</v>
+      </c>
+      <c r="BE319" s="15" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF319" s="15" t="s">
+        <v>1409</v>
+      </c>
+      <c r="BG319" s="19">
+        <v>46219</v>
+      </c>
+      <c r="BH319" s="15" t="s">
+        <v>1403</v>
+      </c>
+      <c r="BI319" s="19">
+        <v>45880</v>
+      </c>
+      <c r="BJ319" s="15">
+        <v>29</v>
+      </c>
+      <c r="BK319" s="15">
+        <v>30</v>
+      </c>
+      <c r="BL319" s="15" t="s">
+        <v>1301</v>
+      </c>
+      <c r="BM319" s="15" t="s">
+        <v>1332</v>
+      </c>
+      <c r="BN319" s="19">
+        <v>46219</v>
+      </c>
+      <c r="BO319" s="15">
+        <v>108</v>
+      </c>
+      <c r="BP319" s="15"/>
+      <c r="BQ319" s="15"/>
+      <c r="BR319" s="15" t="s">
+        <v>1667</v>
+      </c>
+      <c r="BS319" s="19">
+        <v>45952</v>
+      </c>
+      <c r="BT319" s="15" t="s">
+        <v>1433</v>
+      </c>
+      <c r="BU319" s="15">
+        <v>2025</v>
+      </c>
+      <c r="BV319" s="15"/>
+      <c r="BW319" s="15"/>
+      <c r="BX319" s="15">
+        <v>11</v>
+      </c>
+      <c r="BY319" s="20">
+        <v>11</v>
+      </c>
+      <c r="BZ319" s="15" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA319" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB319" s="15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="CC319" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="CD319" s="15" t="s">
+        <v>1349</v>
+      </c>
+      <c r="CE319" s="15" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF319" s="22" t="s">
+        <v>1350</v>
+      </c>
+      <c r="CG319" s="23">
+        <v>787229.2</v>
+      </c>
+    </row>
+    <row r="320" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A320" s="7" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B320" s="7" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C320" s="7" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D320" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="E320" s="7" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F320" s="10" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G320" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H320" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I320" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J320" s="7" t="s">
+        <v>961</v>
+      </c>
+      <c r="K320" s="7"/>
+      <c r="L320" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M320" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N320" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O320" s="12" t="s">
+        <v>1311</v>
+      </c>
+      <c r="P320" s="13">
+        <v>45818</v>
+      </c>
+      <c r="Q320" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="R320" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S320" s="12" t="s">
+        <v>1313</v>
+      </c>
+      <c r="T320" s="12" t="s">
+        <v>1314</v>
+      </c>
+      <c r="U320" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V320" s="13">
+        <v>45818</v>
+      </c>
+      <c r="W320" s="13">
+        <v>45818</v>
+      </c>
+      <c r="X320" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y320" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z320" s="13">
+        <v>45818</v>
+      </c>
+      <c r="AA320" s="13">
+        <v>45818</v>
+      </c>
+      <c r="AB320" s="12" t="s">
+        <v>1405</v>
+      </c>
+      <c r="AC320" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD320" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE320" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF320" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG320" s="12" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH320" s="12" t="s">
+        <v>1336</v>
+      </c>
+      <c r="AI320" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ320" s="13">
+        <v>45821</v>
+      </c>
+      <c r="AK320" s="13">
+        <v>45821</v>
+      </c>
+      <c r="AL320" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM320" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN320" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO320" s="12">
+        <v>3</v>
+      </c>
+      <c r="AP320" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AQ320" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR320" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS320" s="14">
+        <v>0</v>
+      </c>
+      <c r="AT320" s="12">
+        <v>6</v>
+      </c>
+      <c r="AU320" s="15">
+        <v>0</v>
+      </c>
+      <c r="AV320" s="15">
+        <v>-1</v>
+      </c>
+      <c r="AW320" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX320" s="15">
+        <v>0</v>
+      </c>
+      <c r="AY320" s="12">
+        <v>6</v>
+      </c>
+      <c r="AZ320" s="12">
+        <v>9</v>
+      </c>
+      <c r="BA320" s="14">
+        <v>9</v>
+      </c>
+      <c r="BB320" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC320" s="16" t="s">
+        <v>1415</v>
+      </c>
+      <c r="BD320" s="13">
+        <v>45832</v>
+      </c>
+      <c r="BE320" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF320" s="12" t="s">
+        <v>1415</v>
+      </c>
+      <c r="BG320" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BH320" s="12" t="s">
+        <v>1403</v>
+      </c>
+      <c r="BI320" s="13">
+        <v>45880</v>
+      </c>
+      <c r="BJ320" s="12">
+        <v>33</v>
+      </c>
+      <c r="BK320" s="12">
+        <v>33</v>
+      </c>
+      <c r="BL320" s="12" t="s">
+        <v>1327</v>
+      </c>
+      <c r="BM320" s="12"/>
+      <c r="BN320" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BO320" s="15">
+        <v>117</v>
+      </c>
+      <c r="BP320" s="15"/>
+      <c r="BQ320" s="15"/>
+      <c r="BR320" s="15" t="s">
+        <v>1685</v>
+      </c>
+      <c r="BS320" s="19">
+        <v>45961</v>
+      </c>
+      <c r="BT320" s="15" t="s">
+        <v>1303</v>
+      </c>
+      <c r="BU320" s="15">
+        <v>2025</v>
+      </c>
+      <c r="BV320" s="15"/>
+      <c r="BW320" s="15"/>
+      <c r="BX320" s="15">
+        <v>11</v>
+      </c>
+      <c r="BY320" s="20">
+        <v>11</v>
+      </c>
+      <c r="BZ320" s="15" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA320" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB320" s="15" t="s">
+        <v>1686</v>
+      </c>
+      <c r="CC320" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="CD320" s="15" t="s">
+        <v>1349</v>
+      </c>
+      <c r="CE320" s="15" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF320" s="22" t="s">
+        <v>1350</v>
+      </c>
+      <c r="CG320" s="23">
+        <v>787238.2</v>
+      </c>
+    </row>
+    <row r="321" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A321" s="7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B321" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C321" s="7" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D321" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E321" s="7" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F321" s="10" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G321" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H321" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I321" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J321" s="7" t="s">
+        <v>1155</v>
+      </c>
+      <c r="K321" s="7"/>
+      <c r="L321" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M321" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N321" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O321" s="12" t="s">
+        <v>1311</v>
+      </c>
+      <c r="P321" s="13">
+        <v>45789</v>
+      </c>
+      <c r="Q321" s="12" t="s">
+        <v>1286</v>
+      </c>
+      <c r="R321" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S321" s="12" t="s">
+        <v>1287</v>
+      </c>
+      <c r="T321" s="12" t="s">
+        <v>1314</v>
+      </c>
+      <c r="U321" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V321" s="13">
+        <v>45812</v>
+      </c>
+      <c r="W321" s="13">
+        <v>45812</v>
+      </c>
+      <c r="X321" s="12">
+        <v>17</v>
+      </c>
+      <c r="Y321" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z321" s="13">
+        <v>45812</v>
+      </c>
+      <c r="AA321" s="13">
+        <v>45812</v>
+      </c>
+      <c r="AB321" s="12" t="s">
+        <v>1355</v>
+      </c>
+      <c r="AC321" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD321" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE321" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF321" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG321" s="12" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH321" s="12" t="s">
+        <v>1339</v>
+      </c>
+      <c r="AI321" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ321" s="13">
+        <v>45821</v>
+      </c>
+      <c r="AK321" s="13">
+        <v>45821</v>
+      </c>
+      <c r="AL321" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM321" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN321" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO321" s="12">
+        <v>7</v>
+      </c>
+      <c r="AP321" s="15" t="s">
+        <v>1370</v>
+      </c>
+      <c r="AQ321" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR321" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS321" s="14">
+        <v>0</v>
+      </c>
+      <c r="AT321" s="12">
+        <v>19</v>
+      </c>
+      <c r="AU321" s="15">
+        <v>0</v>
+      </c>
+      <c r="AV321" s="15">
+        <v>0</v>
+      </c>
+      <c r="AW321" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX321" s="15">
+        <v>0</v>
+      </c>
+      <c r="AY321" s="12">
+        <v>19</v>
+      </c>
+      <c r="AZ321" s="12">
+        <v>26</v>
+      </c>
+      <c r="BA321" s="14">
+        <v>26</v>
+      </c>
+      <c r="BB321" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC321" s="16" t="s">
+        <v>1371</v>
+      </c>
+      <c r="BD321" s="13">
+        <v>45849</v>
+      </c>
+      <c r="BE321" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF321" s="12" t="s">
+        <v>1371</v>
+      </c>
+      <c r="BG321" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BH321" s="12" t="s">
+        <v>1364</v>
+      </c>
+      <c r="BI321" s="13">
+        <v>45852</v>
+      </c>
+      <c r="BJ321" s="12">
+        <v>1</v>
+      </c>
+      <c r="BK321" s="12">
+        <v>18</v>
+      </c>
+      <c r="BL321" s="12" t="s">
+        <v>1327</v>
+      </c>
+      <c r="BM321" s="12"/>
+      <c r="BN321" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BO321" s="15">
+        <v>145</v>
+      </c>
+      <c r="BP321" s="15"/>
+      <c r="BQ321" s="15"/>
+      <c r="BR321" s="15" t="s">
+        <v>1741</v>
+      </c>
+      <c r="BS321" s="19">
+        <v>45989</v>
+      </c>
+      <c r="BT321" s="15" t="s">
+        <v>1454</v>
+      </c>
+      <c r="BU321" s="15">
+        <v>2025</v>
+      </c>
+      <c r="BV321" s="15"/>
+      <c r="BW321" s="15"/>
+      <c r="BX321" s="15">
+        <v>11</v>
+      </c>
+      <c r="BY321" s="20">
+        <v>11</v>
+      </c>
+      <c r="BZ321" s="15" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA321" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB321" s="15" t="s">
+        <v>1742</v>
+      </c>
+      <c r="CC321" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="CD321" s="15" t="s">
+        <v>1349</v>
+      </c>
+      <c r="CE321" s="15" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF321" s="22" t="s">
+        <v>1350</v>
+      </c>
+      <c r="CG321" s="23">
+        <v>787266.2</v>
+      </c>
+    </row>
+    <row r="322" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A322" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D322" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E322" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F322" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G322" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H322" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I322" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J322" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K322" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="L322" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M322" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N322" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O322" s="12" t="s">
+        <v>1285</v>
+      </c>
+      <c r="P322" s="13">
+        <v>45807</v>
+      </c>
+      <c r="Q322" s="12" t="s">
+        <v>1286</v>
+      </c>
+      <c r="R322" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S322" s="12" t="s">
+        <v>1287</v>
+      </c>
+      <c r="T322" s="12" t="s">
+        <v>1314</v>
+      </c>
+      <c r="U322" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V322" s="13">
+        <v>45812</v>
+      </c>
+      <c r="W322" s="13">
+        <v>45812</v>
+      </c>
+      <c r="X322" s="12">
+        <v>3</v>
+      </c>
+      <c r="Y322" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z322" s="13">
+        <v>45812</v>
+      </c>
+      <c r="AA322" s="13">
+        <v>45812</v>
+      </c>
+      <c r="AB322" s="12" t="s">
+        <v>1355</v>
+      </c>
+      <c r="AC322" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD322" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE322" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF322" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG322" s="12" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH322" s="12" t="s">
+        <v>1330</v>
+      </c>
+      <c r="AI322" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ322" s="13">
+        <v>45813</v>
+      </c>
+      <c r="AK322" s="13">
+        <v>45813</v>
+      </c>
+      <c r="AL322" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM322" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN322" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO322" s="12">
+        <v>1</v>
+      </c>
+      <c r="AP322" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AQ322" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR322" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS322" s="14">
+        <v>26</v>
+      </c>
+      <c r="AT322" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU322" s="15">
+        <v>26</v>
+      </c>
+      <c r="AV322" s="15">
+        <v>0</v>
+      </c>
+      <c r="AW322" s="12">
+        <v>26</v>
+      </c>
+      <c r="AX322" s="15">
+        <v>26</v>
+      </c>
+      <c r="AY322" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ322" s="12">
+        <v>27</v>
+      </c>
+      <c r="BA322" s="14">
+        <v>27</v>
+      </c>
+      <c r="BB322" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC322" s="16" t="s">
+        <v>1364</v>
+      </c>
+      <c r="BD322" s="13">
+        <v>45852</v>
+      </c>
+      <c r="BE322" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF322" s="12" t="s">
+        <v>1364</v>
+      </c>
+      <c r="BG322" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BH322" s="12" t="s">
+        <v>1364</v>
+      </c>
+      <c r="BI322" s="13">
+        <v>45852</v>
+      </c>
+      <c r="BJ322" s="12">
+        <v>0</v>
+      </c>
+      <c r="BK322" s="12">
+        <v>3</v>
+      </c>
+      <c r="BL322" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="BM322" s="12" t="s">
+        <v>1365</v>
+      </c>
+      <c r="BN322" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BO322" s="12">
+        <v>7</v>
+      </c>
+      <c r="BP322" s="12"/>
+      <c r="BQ322" s="12"/>
+      <c r="BR322" s="12" t="s">
+        <v>1365</v>
+      </c>
+      <c r="BS322" s="13">
+        <v>45861</v>
+      </c>
+      <c r="BT322" s="12" t="s">
+        <v>1328</v>
+      </c>
+      <c r="BU322" s="12">
+        <v>2025</v>
+      </c>
+      <c r="BV322" s="12"/>
+      <c r="BW322" s="12"/>
+      <c r="BX322" s="12">
+        <v>10</v>
+      </c>
+      <c r="BY322" s="14">
+        <v>38</v>
+      </c>
+      <c r="BZ322" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA322" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB322" s="12" t="s">
+        <v>1304</v>
+      </c>
+      <c r="CC322" s="12" t="s">
+        <v>1347</v>
+      </c>
+      <c r="CD322" s="12" t="s">
+        <v>1366</v>
+      </c>
+      <c r="CE322" s="12" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF322" s="17" t="s">
+        <v>1367</v>
+      </c>
+      <c r="CG322" s="18">
+        <v>104054.53</v>
+      </c>
+      <c r="CH322" s="18">
+        <v>3926.59</v>
+      </c>
+      <c r="CI322" s="15" t="s">
+        <v>1310</v>
+      </c>
+      <c r="CJ322" s="12" t="s">
+        <v>1310</v>
+      </c>
+      <c r="CK322" s="15" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="323" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A323" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="B323" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C323" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="D323" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E323" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F323" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="G323" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H323" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I323" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J323" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="K323" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="L323" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M323" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N323" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O323" s="12" t="s">
+        <v>1311</v>
+      </c>
+      <c r="P323" s="13">
+        <v>45821</v>
+      </c>
+      <c r="Q323" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="R323" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S323" s="12" t="s">
+        <v>1463</v>
+      </c>
+      <c r="T323" s="12" t="s">
+        <v>1288</v>
+      </c>
+      <c r="U323" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V323" s="13">
+        <v>45824</v>
+      </c>
+      <c r="W323" s="13">
+        <v>45824</v>
+      </c>
+      <c r="X323" s="12">
+        <v>1</v>
+      </c>
+      <c r="Y323" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z323" s="13">
+        <v>45824</v>
+      </c>
+      <c r="AA323" s="13">
+        <v>45824</v>
+      </c>
+      <c r="AB323" s="12" t="s">
+        <v>1442</v>
+      </c>
+      <c r="AC323" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD323" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE323" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF323" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG323" s="12" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH323" s="12" t="s">
+        <v>1296</v>
+      </c>
+      <c r="AI323" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ323" s="13">
+        <v>45824</v>
+      </c>
+      <c r="AK323" s="13">
+        <v>45824</v>
+      </c>
+      <c r="AL323" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM323" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN323" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO323" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP323" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AQ323" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR323" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS323" s="14" t="s">
+        <v>1299</v>
+      </c>
+      <c r="AT323" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU323" s="15">
+        <v>0</v>
+      </c>
+      <c r="AV323" s="15">
+        <v>0</v>
+      </c>
+      <c r="AW323" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX323" s="15">
+        <v>0</v>
+      </c>
+      <c r="AY323" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ323" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA323" s="14">
+        <v>0</v>
+      </c>
+      <c r="BB323" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC323" s="16" t="s">
+        <v>1377</v>
+      </c>
+      <c r="BD323" s="13">
+        <v>45824</v>
+      </c>
+      <c r="BE323" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF323" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="BG323" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BH323" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="BI323" s="13">
+        <v>45824</v>
+      </c>
+      <c r="BJ323" s="12">
+        <v>0</v>
+      </c>
+      <c r="BK323" s="12">
+        <v>1</v>
+      </c>
+      <c r="BL323" s="15" t="s">
+        <v>1327</v>
+      </c>
+      <c r="BM323" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="BN323" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BO323" s="12">
+        <v>0</v>
+      </c>
+      <c r="BP323" s="12"/>
+      <c r="BQ323" s="12"/>
+      <c r="BR323" s="12"/>
+      <c r="BS323" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BT323" s="12" t="s">
+        <v>1328</v>
+      </c>
+      <c r="BU323" s="12">
+        <v>2026</v>
+      </c>
+      <c r="BV323" s="12"/>
+      <c r="BW323" s="12"/>
+      <c r="BX323" s="12">
+        <v>1</v>
+      </c>
+      <c r="BY323" s="14">
+        <v>1</v>
+      </c>
+      <c r="BZ323" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA323" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB323" s="12" t="s">
+        <v>1441</v>
+      </c>
+      <c r="CC323" s="12" t="s">
+        <v>1319</v>
+      </c>
+      <c r="CD323" s="12" t="s">
+        <v>1349</v>
+      </c>
+      <c r="CE323" s="12" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF323" s="17" t="s">
+        <v>1350</v>
+      </c>
+      <c r="CG323" s="18">
+        <v>1288544.3999999999</v>
+      </c>
+      <c r="CH323" s="18">
+        <v>343.06</v>
+      </c>
+      <c r="CI323" s="15" t="s">
+        <v>1309</v>
+      </c>
+      <c r="CJ323" s="12" t="s">
+        <v>1310</v>
+      </c>
+      <c r="CK323" s="15" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="324" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A324" s="7" t="s">
+        <v>981</v>
+      </c>
+      <c r="B324" s="7" t="s">
+        <v>982</v>
+      </c>
+      <c r="C324" s="7" t="s">
+        <v>983</v>
+      </c>
+      <c r="D324" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="E324" s="9" t="s">
+        <v>786</v>
+      </c>
+      <c r="F324" s="10" t="s">
+        <v>984</v>
+      </c>
+      <c r="G324" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H324" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I324" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J324" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="K324" s="7" t="s">
+        <v>985</v>
+      </c>
+      <c r="L324" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M324" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N324" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O324" s="15" t="s">
+        <v>1285</v>
+      </c>
+      <c r="P324" s="19">
+        <v>45817</v>
+      </c>
+      <c r="Q324" s="15" t="s">
+        <v>1312</v>
+      </c>
+      <c r="R324" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S324" s="15" t="s">
+        <v>1313</v>
+      </c>
+      <c r="T324" s="15" t="s">
+        <v>1314</v>
+      </c>
+      <c r="U324" s="15" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V324" s="19">
+        <v>45818</v>
+      </c>
+      <c r="W324" s="19">
+        <v>45818</v>
+      </c>
+      <c r="X324" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y324" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z324" s="19">
+        <v>45818</v>
+      </c>
+      <c r="AA324" s="19">
+        <v>45818</v>
+      </c>
+      <c r="AB324" s="15" t="s">
+        <v>1405</v>
+      </c>
+      <c r="AC324" s="15" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD324" s="15" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE324" s="15" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF324" s="20">
+        <v>0</v>
+      </c>
+      <c r="AG324" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH324" s="15" t="s">
+        <v>1330</v>
+      </c>
+      <c r="AI324" s="15" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ324" s="19">
+        <v>45819</v>
+      </c>
+      <c r="AK324" s="19">
+        <v>45819</v>
+      </c>
+      <c r="AL324" s="15" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM324" s="15" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN324" s="15" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO324" s="15">
+        <v>1</v>
+      </c>
+      <c r="AP324" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AQ324" s="15" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR324" s="15">
+        <v>0</v>
+      </c>
+      <c r="AS324" s="20">
+        <v>0</v>
+      </c>
+      <c r="AT324" s="15">
+        <v>13</v>
+      </c>
+      <c r="AU324" s="15">
+        <v>0</v>
+      </c>
+      <c r="AV324" s="15">
+        <v>0</v>
+      </c>
+      <c r="AW324" s="15">
+        <v>0</v>
+      </c>
+      <c r="AX324" s="15">
+        <v>0</v>
+      </c>
+      <c r="AY324" s="15">
+        <v>13</v>
+      </c>
+      <c r="AZ324" s="15">
+        <v>14</v>
+      </c>
+      <c r="BA324" s="20">
+        <v>13</v>
+      </c>
+      <c r="BB324" s="15" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC324" s="21" t="s">
+        <v>1409</v>
+      </c>
+      <c r="BD324" s="19">
+        <v>45838</v>
+      </c>
+      <c r="BE324" s="15" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF324" s="15" t="s">
+        <v>1409</v>
+      </c>
+      <c r="BG324" s="19">
+        <v>46219</v>
+      </c>
+      <c r="BH324" s="15" t="s">
+        <v>1403</v>
+      </c>
+      <c r="BI324" s="19">
+        <v>45880</v>
+      </c>
+      <c r="BJ324" s="15">
+        <v>29</v>
+      </c>
+      <c r="BK324" s="15">
+        <v>30</v>
+      </c>
+      <c r="BL324" s="15" t="s">
+        <v>1301</v>
+      </c>
+      <c r="BM324" s="15" t="s">
+        <v>1332</v>
+      </c>
+      <c r="BN324" s="19">
+        <v>46219</v>
+      </c>
+      <c r="BO324" s="15">
+        <v>108</v>
+      </c>
+      <c r="BP324" s="15"/>
+      <c r="BQ324" s="15"/>
+      <c r="BR324" s="15" t="s">
+        <v>1667</v>
+      </c>
+      <c r="BS324" s="19">
+        <v>45952</v>
+      </c>
+      <c r="BT324" s="15" t="s">
+        <v>1433</v>
+      </c>
+      <c r="BU324" s="15">
+        <v>2025</v>
+      </c>
+      <c r="BV324" s="15"/>
+      <c r="BW324" s="15"/>
+      <c r="BX324" s="15">
+        <v>11</v>
+      </c>
+      <c r="BY324" s="20">
+        <v>11</v>
+      </c>
+      <c r="BZ324" s="15" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA324" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB324" s="15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="CC324" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="CD324" s="15" t="s">
+        <v>1349</v>
+      </c>
+      <c r="CE324" s="15" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF324" s="22" t="s">
+        <v>1350</v>
+      </c>
+      <c r="CG324" s="23">
+        <v>787229.2</v>
+      </c>
+    </row>
+    <row r="325" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A325" s="7" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B325" s="7" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C325" s="7" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D325" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="E325" s="7" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F325" s="10" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G325" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H325" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I325" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J325" s="7" t="s">
+        <v>961</v>
+      </c>
+      <c r="K325" s="7"/>
+      <c r="L325" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M325" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N325" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O325" s="12" t="s">
+        <v>1311</v>
+      </c>
+      <c r="P325" s="13">
+        <v>45818</v>
+      </c>
+      <c r="Q325" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="R325" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S325" s="12" t="s">
+        <v>1313</v>
+      </c>
+      <c r="T325" s="12" t="s">
+        <v>1314</v>
+      </c>
+      <c r="U325" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V325" s="13">
+        <v>45818</v>
+      </c>
+      <c r="W325" s="13">
+        <v>45818</v>
+      </c>
+      <c r="X325" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y325" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z325" s="13">
+        <v>45818</v>
+      </c>
+      <c r="AA325" s="13">
+        <v>45818</v>
+      </c>
+      <c r="AB325" s="12" t="s">
+        <v>1405</v>
+      </c>
+      <c r="AC325" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD325" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE325" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF325" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG325" s="12" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH325" s="12" t="s">
+        <v>1336</v>
+      </c>
+      <c r="AI325" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ325" s="13">
+        <v>45821</v>
+      </c>
+      <c r="AK325" s="13">
+        <v>45821</v>
+      </c>
+      <c r="AL325" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM325" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN325" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO325" s="12">
+        <v>3</v>
+      </c>
+      <c r="AP325" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AQ325" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR325" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS325" s="14">
+        <v>0</v>
+      </c>
+      <c r="AT325" s="12">
+        <v>6</v>
+      </c>
+      <c r="AU325" s="15">
+        <v>0</v>
+      </c>
+      <c r="AV325" s="15">
+        <v>-1</v>
+      </c>
+      <c r="AW325" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX325" s="15">
+        <v>0</v>
+      </c>
+      <c r="AY325" s="12">
+        <v>6</v>
+      </c>
+      <c r="AZ325" s="12">
+        <v>9</v>
+      </c>
+      <c r="BA325" s="14">
+        <v>9</v>
+      </c>
+      <c r="BB325" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC325" s="16" t="s">
+        <v>1415</v>
+      </c>
+      <c r="BD325" s="13">
+        <v>45832</v>
+      </c>
+      <c r="BE325" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF325" s="12" t="s">
+        <v>1415</v>
+      </c>
+      <c r="BG325" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BH325" s="12" t="s">
+        <v>1403</v>
+      </c>
+      <c r="BI325" s="13">
+        <v>45880</v>
+      </c>
+      <c r="BJ325" s="12">
+        <v>33</v>
+      </c>
+      <c r="BK325" s="12">
+        <v>33</v>
+      </c>
+      <c r="BL325" s="12" t="s">
+        <v>1327</v>
+      </c>
+      <c r="BM325" s="12"/>
+      <c r="BN325" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BO325" s="15">
+        <v>117</v>
+      </c>
+      <c r="BP325" s="15"/>
+      <c r="BQ325" s="15"/>
+      <c r="BR325" s="15" t="s">
+        <v>1685</v>
+      </c>
+      <c r="BS325" s="19">
+        <v>45961</v>
+      </c>
+      <c r="BT325" s="15" t="s">
+        <v>1303</v>
+      </c>
+      <c r="BU325" s="15">
+        <v>2025</v>
+      </c>
+      <c r="BV325" s="15"/>
+      <c r="BW325" s="15"/>
+      <c r="BX325" s="15">
+        <v>11</v>
+      </c>
+      <c r="BY325" s="20">
+        <v>11</v>
+      </c>
+      <c r="BZ325" s="15" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA325" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB325" s="15" t="s">
+        <v>1686</v>
+      </c>
+      <c r="CC325" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="CD325" s="15" t="s">
+        <v>1349</v>
+      </c>
+      <c r="CE325" s="15" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF325" s="22" t="s">
+        <v>1350</v>
+      </c>
+      <c r="CG325" s="23">
+        <v>787238.2</v>
+      </c>
+    </row>
+    <row r="326" spans="1:89" x14ac:dyDescent="0.35">
+      <c r="A326" s="7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B326" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C326" s="7" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D326" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E326" s="7" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F326" s="10" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G326" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H326" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I326" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J326" s="7" t="s">
+        <v>1155</v>
+      </c>
+      <c r="K326" s="7"/>
+      <c r="L326" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M326" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N326" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O326" s="12" t="s">
+        <v>1311</v>
+      </c>
+      <c r="P326" s="13">
+        <v>45789</v>
+      </c>
+      <c r="Q326" s="12" t="s">
+        <v>1286</v>
+      </c>
+      <c r="R326" s="12">
+        <v>2025</v>
+      </c>
+      <c r="S326" s="12" t="s">
+        <v>1287</v>
+      </c>
+      <c r="T326" s="12" t="s">
+        <v>1314</v>
+      </c>
+      <c r="U326" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V326" s="13">
+        <v>45812</v>
+      </c>
+      <c r="W326" s="13">
+        <v>45812</v>
+      </c>
+      <c r="X326" s="12">
+        <v>17</v>
+      </c>
+      <c r="Y326" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Z326" s="13">
+        <v>45812</v>
+      </c>
+      <c r="AA326" s="13">
+        <v>45812</v>
+      </c>
+      <c r="AB326" s="12" t="s">
+        <v>1355</v>
+      </c>
+      <c r="AC326" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AD326" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AE326" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AF326" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG326" s="12" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AH326" s="12" t="s">
+        <v>1339</v>
+      </c>
+      <c r="AI326" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AJ326" s="13">
+        <v>45821</v>
+      </c>
+      <c r="AK326" s="13">
+        <v>45821</v>
+      </c>
+      <c r="AL326" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AM326" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AN326" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AO326" s="12">
+        <v>7</v>
+      </c>
+      <c r="AP326" s="15" t="s">
+        <v>1370</v>
+      </c>
+      <c r="AQ326" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR326" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS326" s="14">
+        <v>0</v>
+      </c>
+      <c r="AT326" s="12">
+        <v>19</v>
+      </c>
+      <c r="AU326" s="15">
+        <v>0</v>
+      </c>
+      <c r="AV326" s="15">
+        <v>0</v>
+      </c>
+      <c r="AW326" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX326" s="15">
+        <v>0</v>
+      </c>
+      <c r="AY326" s="12">
+        <v>19</v>
+      </c>
+      <c r="AZ326" s="12">
+        <v>26</v>
+      </c>
+      <c r="BA326" s="14">
+        <v>26</v>
+      </c>
+      <c r="BB326" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="BC326" s="16" t="s">
+        <v>1371</v>
+      </c>
+      <c r="BD326" s="13">
+        <v>45849</v>
+      </c>
+      <c r="BE326" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BF326" s="12" t="s">
+        <v>1371</v>
+      </c>
+      <c r="BG326" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BH326" s="12" t="s">
+        <v>1364</v>
+      </c>
+      <c r="BI326" s="13">
+        <v>45852</v>
+      </c>
+      <c r="BJ326" s="12">
+        <v>1</v>
+      </c>
+      <c r="BK326" s="12">
+        <v>18</v>
+      </c>
+      <c r="BL326" s="12" t="s">
+        <v>1327</v>
+      </c>
+      <c r="BM326" s="12"/>
+      <c r="BN326" s="13">
+        <v>46219</v>
+      </c>
+      <c r="BO326" s="15">
+        <v>145</v>
+      </c>
+      <c r="BP326" s="15"/>
+      <c r="BQ326" s="15"/>
+      <c r="BR326" s="15" t="s">
+        <v>1741</v>
+      </c>
+      <c r="BS326" s="19">
+        <v>45989</v>
+      </c>
+      <c r="BT326" s="15" t="s">
+        <v>1454</v>
+      </c>
+      <c r="BU326" s="15">
+        <v>2025</v>
+      </c>
+      <c r="BV326" s="15"/>
+      <c r="BW326" s="15"/>
+      <c r="BX326" s="15">
+        <v>11</v>
+      </c>
+      <c r="BY326" s="20">
+        <v>11</v>
+      </c>
+      <c r="BZ326" s="15" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CA326" s="15" t="s">
+        <v>1290</v>
+      </c>
+      <c r="CB326" s="15" t="s">
+        <v>1742</v>
+      </c>
+      <c r="CC326" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="CD326" s="15" t="s">
+        <v>1349</v>
+      </c>
+      <c r="CE326" s="15" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CF326" s="22" t="s">
+        <v>1350</v>
+      </c>
+      <c r="CG326" s="23">
+        <v>787266.2</v>
       </c>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A1:N2 A260:N260 O1:CH1 A264:F264 H264:N264 CH129:CK129 CH133:CK133 CH163:CK163 CH167:CK167 CH169:CK169 CH171:CK171 CH176:CK176 CH178:CK179 CH192:CK192 CH212:CK212 CH219:CK219 CH222:CK223 CH225:CK231 CH233:CK234 CH249:CK249 O2:CK111 O112:CG268 CH261:CK268 O269:CK277 O278:CG280 O281:CK282 O283:CG285 O286:CK287 O288:CG290 O291:CK298 O299:BN306" name="All Access Jorge H" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A1:N2 A260:N260 O1:CH1 A264:F264 H264:N264 CH129:CK129 CH133:CK133 CH163:CK163 CH167:CK167 CH169:CK169 CH171:CK171 CH176:CK176 CH178:CK179 CH192:CK192 CH212:CK212 CH219:CK219 CH222:CK223 CH225:CK231 CH233:CK234 CH249:CK249 O2:CK111 O112:CG268 CH261:CK268 O269:CK277 O278:CG280 O281:CK282 O283:CG285 O286:CK287 O288:CG290 O291:CK298 O299:BN306 O307:CK308 O309:CG311 O312:CK313 O314:CG316 O317:CK318 O319:CG321 O322:CK323 O324:CG326" name="All Access Jorge H" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A3:N5" name="All Access Jorge H_1" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A6:N6" name="All Access Jorge H_2" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A7:N9" name="All Access Jorge H_3" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A10:N10" name="All Access Jorge H_4" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A11:N13" name="All Access Jorge H_5" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A14:N15" name="All Access Jorge H_6" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
-    <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A16:N16 A276:N276 A281:N281 A286:N286" name="All Access Jorge H_7" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A16:N16 A276:N276 A281:N281 A286:N286 A307:N307 A312:N312 A317:N317 A322:N322" name="All Access Jorge H_7" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A17:N18" name="All Access Jorge H_8" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A19:N23" name="All Access Jorge H_9" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A24:N24" name="All Access Jorge H_10" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
@@ -83067,7 +88103,7 @@
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A61:N67" name="All Access Jorge H_18" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A68:N73" name="All Access Jorge H_19" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A74:N77" name="All Access Jorge H_20" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
-    <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A78:N83 A265:N275 A277:N277 A282:N282 A287:N287 A291:N306" name="All Access Jorge H_21" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A78:N83 A265:N275 A277:N277 A282:N282 A287:N287 A291:N306 A308:N308 A313:N313 A318:N318 A323:N323" name="All Access Jorge H_21" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A84:N84" name="All Access Jorge H_22" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A85:N87" name="All Access Jorge H_23" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A88:N89" name="All Access Jorge H_24" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
@@ -83126,11 +88162,11 @@
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A206:N206" name="All Access Jorge H_77" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A207:N208" name="All Access Jorge H_78" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A209:N209" name="All Access Jorge H_79" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
-    <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A210:N211 A278:N278 A283:N283 A288:N288" name="All Access Jorge H_80" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A210:N211 A278:N278 A283:N283 A288:N288 A309:N309 A314:N314 A319:N319 A324:N324" name="All Access Jorge H_80" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A212:N212" name="All Access Jorge H_81" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A213:N213" name="All Access Jorge H_82" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A214:N218" name="All Access Jorge H_83" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
-    <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A219:N220 A279:N279 A284:N284 A289:N289" name="All Access Jorge H_84" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A219:N220 A279:N279 A284:N284 A289:N289 A310:N310 A315:N315 A320:N320 A325:N325" name="All Access Jorge H_84" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A221:N221" name="All Access Jorge H_85" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A222:N227" name="All Access Jorge H_86" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A228:N231" name="All Access Jorge H_87" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
@@ -83141,16 +88177,16 @@
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A241:N241" name="All Access Jorge H_92" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A242:N243" name="All Access Jorge H_93" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A244:N247" name="All Access Jorge H_94" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
-    <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A248:N248 A280:N280 A285:N285 A290:N290" name="All Access Jorge H_95" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A248:N248 A280:N280 A285:N285 A290:N290 A311:N311 A316:N316 A321:N321 A326:N326" name="All Access Jorge H_95" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A249:N249 G261:G264" name="All Access Jorge H_96" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A250:N257 A261:F261 H261:N261" name="All Access Jorge H_97" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A258:N258 A262:F262 H262:N262" name="All Access Jorge H_98" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A259:N259 A263:F263 H263:N263" name="All Access Jorge H_99" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
   </protectedRanges>
-  <autoFilter ref="A1:CK290" xr:uid="{5A45D9DC-E8AF-436A-91D0-388125A4A950}">
+  <autoFilter ref="A1:CK306" xr:uid="{5A45D9DC-E8AF-436A-91D0-388125A4A950}">
     <filterColumn colId="6">
       <filters>
-        <filter val="Vencido"/>
+        <filter val="Cerrado"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/public/sampleData.xlsx
+++ b/public/sampleData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U45555\IT-dashboard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D82B5FF-91C6-4D90-9C89-9A24B08035B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5D08D8-F38A-4775-84A6-2C0BB3066CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{724309DC-2642-42C3-9093-42F88D91BE1B}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$CK$306</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$CK$326</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5842,7 +5842,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A45D9DC-E8AF-436A-91D0-388125A4A950}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:CK326"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -6165,7 +6164,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="2" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -6426,7 +6425,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="3" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>27</v>
       </c>
@@ -6687,7 +6686,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="4" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>39</v>
       </c>
@@ -6948,7 +6947,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="5" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>44</v>
       </c>
@@ -7205,7 +7204,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="6" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>48</v>
       </c>
@@ -7466,7 +7465,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="7" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>55</v>
       </c>
@@ -7721,7 +7720,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="8" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>60</v>
       </c>
@@ -7980,7 +7979,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="9" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>64</v>
       </c>
@@ -8241,7 +8240,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="10" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>72</v>
       </c>
@@ -8500,7 +8499,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="11" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>79</v>
       </c>
@@ -8759,7 +8758,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="12" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>84</v>
       </c>
@@ -9020,7 +9019,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="13" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>89</v>
       </c>
@@ -9275,7 +9274,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="14" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>93</v>
       </c>
@@ -9536,7 +9535,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="15" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>98</v>
       </c>
@@ -10052,7 +10051,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="17" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>107</v>
       </c>
@@ -10313,7 +10312,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="18" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>116</v>
       </c>
@@ -10570,7 +10569,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="19" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>120</v>
       </c>
@@ -10831,7 +10830,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="20" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>127</v>
       </c>
@@ -11092,7 +11091,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="21" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>134</v>
       </c>
@@ -11353,7 +11352,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="22" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>143</v>
       </c>
@@ -11610,7 +11609,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="23" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>148</v>
       </c>
@@ -11869,7 +11868,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="24" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>155</v>
       </c>
@@ -12130,7 +12129,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="25" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>161</v>
       </c>
@@ -12383,7 +12382,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="26" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>166</v>
       </c>
@@ -12644,7 +12643,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="27" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>170</v>
       </c>
@@ -12905,7 +12904,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="28" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>174</v>
       </c>
@@ -13162,7 +13161,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="29" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>178</v>
       </c>
@@ -13423,7 +13422,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="30" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>183</v>
       </c>
@@ -13682,7 +13681,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="31" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>187</v>
       </c>
@@ -13939,7 +13938,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="32" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>194</v>
       </c>
@@ -14190,7 +14189,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="33" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>199</v>
       </c>
@@ -14451,7 +14450,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="34" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>205</v>
       </c>
@@ -14708,7 +14707,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="35" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>209</v>
       </c>
@@ -14965,7 +14964,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="36" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>213</v>
       </c>
@@ -15220,7 +15219,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="37" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>217</v>
       </c>
@@ -15481,7 +15480,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="38" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>221</v>
       </c>
@@ -15742,7 +15741,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="39" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>225</v>
       </c>
@@ -16003,7 +16002,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="40" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
         <v>229</v>
       </c>
@@ -16256,7 +16255,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="41" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>233</v>
       </c>
@@ -16507,7 +16506,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="42" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
         <v>237</v>
       </c>
@@ -16768,7 +16767,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="43" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>241</v>
       </c>
@@ -17029,7 +17028,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="44" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
         <v>245</v>
       </c>
@@ -17286,7 +17285,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="45" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>249</v>
       </c>
@@ -17547,7 +17546,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="46" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>253</v>
       </c>
@@ -17806,7 +17805,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="47" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>257</v>
       </c>
@@ -18065,7 +18064,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="48" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
         <v>262</v>
       </c>
@@ -18326,7 +18325,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="49" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>266</v>
       </c>
@@ -18585,7 +18584,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="50" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
         <v>270</v>
       </c>
@@ -18844,7 +18843,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="51" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>276</v>
       </c>
@@ -19101,7 +19100,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="52" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>280</v>
       </c>
@@ -19358,7 +19357,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="53" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>284</v>
       </c>
@@ -19619,7 +19618,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="54" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A54" s="7" t="s">
         <v>289</v>
       </c>
@@ -19880,7 +19879,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="55" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>294</v>
       </c>
@@ -20135,7 +20134,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="56" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>298</v>
       </c>
@@ -20390,7 +20389,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="57" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A57" s="7" t="s">
         <v>302</v>
       </c>
@@ -20651,7 +20650,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="58" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>306</v>
       </c>
@@ -20912,7 +20911,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="59" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
         <v>310</v>
       </c>
@@ -21173,7 +21172,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="60" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>314</v>
       </c>
@@ -21430,7 +21429,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="61" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>318</v>
       </c>
@@ -21691,7 +21690,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="62" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
         <v>323</v>
       </c>
@@ -21948,7 +21947,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="63" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>329</v>
       </c>
@@ -22205,7 +22204,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="64" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A64" s="7" t="s">
         <v>333</v>
       </c>
@@ -22462,7 +22461,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="65" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>337</v>
       </c>
@@ -22723,7 +22722,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="66" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>341</v>
       </c>
@@ -22984,7 +22983,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="67" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>345</v>
       </c>
@@ -23237,7 +23236,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="68" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A68" s="7" t="s">
         <v>349</v>
       </c>
@@ -23492,7 +23491,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="69" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>356</v>
       </c>
@@ -23745,7 +23744,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="70" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A70" s="7" t="s">
         <v>360</v>
       </c>
@@ -24002,7 +24001,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="71" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>364</v>
       </c>
@@ -24263,7 +24262,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="72" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A72" s="7" t="s">
         <v>369</v>
       </c>
@@ -24524,7 +24523,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="73" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>373</v>
       </c>
@@ -24785,7 +24784,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="74" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>377</v>
       </c>
@@ -25046,7 +25045,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="75" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A75" s="7" t="s">
         <v>381</v>
       </c>
@@ -25307,7 +25306,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="76" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>385</v>
       </c>
@@ -25568,7 +25567,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="77" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
         <v>389</v>
       </c>
@@ -25829,7 +25828,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="78" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A78" s="7" t="s">
         <v>393</v>
       </c>
@@ -26090,7 +26089,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="79" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>397</v>
       </c>
@@ -26351,7 +26350,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="80" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A80" s="7" t="s">
         <v>401</v>
       </c>
@@ -26612,7 +26611,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="81" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>405</v>
       </c>
@@ -27124,7 +27123,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="83" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>413</v>
       </c>
@@ -27379,7 +27378,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="84" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>419</v>
       </c>
@@ -27632,7 +27631,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="85" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>425</v>
       </c>
@@ -27893,7 +27892,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="86" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
         <v>430</v>
       </c>
@@ -28152,7 +28151,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="87" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>433</v>
       </c>
@@ -28409,7 +28408,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="88" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>440</v>
       </c>
@@ -28670,7 +28669,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="89" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A89" s="7" t="s">
         <v>444</v>
       </c>
@@ -28929,7 +28928,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="90" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
         <v>449</v>
       </c>
@@ -29188,7 +29187,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="91" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>454</v>
       </c>
@@ -29449,7 +29448,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="92" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A92" s="7" t="s">
         <v>458</v>
       </c>
@@ -29708,7 +29707,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="93" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>462</v>
       </c>
@@ -29969,7 +29968,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="94" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A94" s="7" t="s">
         <v>470</v>
       </c>
@@ -30230,7 +30229,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="95" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>475</v>
       </c>
@@ -30491,7 +30490,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="96" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
         <v>480</v>
       </c>
@@ -30752,7 +30751,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="97" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>484</v>
       </c>
@@ -31005,7 +31004,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="98" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>488</v>
       </c>
@@ -31258,7 +31257,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="99" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>493</v>
       </c>
@@ -31519,7 +31518,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="100" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A100" s="7" t="s">
         <v>499</v>
       </c>
@@ -31778,7 +31777,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="101" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>503</v>
       </c>
@@ -32039,7 +32038,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="102" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A102" s="7" t="s">
         <v>507</v>
       </c>
@@ -32300,7 +32299,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="103" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>511</v>
       </c>
@@ -32555,7 +32554,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="104" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>515</v>
       </c>
@@ -32816,7 +32815,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="105" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>520</v>
       </c>
@@ -33069,7 +33068,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="106" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A106" s="7" t="s">
         <v>523</v>
       </c>
@@ -33330,7 +33329,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="107" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>527</v>
       </c>
@@ -33585,7 +33584,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="108" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
         <v>531</v>
       </c>
@@ -33840,7 +33839,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="109" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>535</v>
       </c>
@@ -34101,7 +34100,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="110" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A110" s="7" t="s">
         <v>539</v>
       </c>
@@ -34360,7 +34359,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="111" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>543</v>
       </c>
@@ -34621,7 +34620,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="112" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
         <v>547</v>
       </c>
@@ -34870,7 +34869,7 @@
         <v>787130.2</v>
       </c>
     </row>
-    <row r="113" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>551</v>
       </c>
@@ -35119,7 +35118,7 @@
         <v>787131.2</v>
       </c>
     </row>
-    <row r="114" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
         <v>555</v>
       </c>
@@ -35368,7 +35367,7 @@
         <v>787132.2</v>
       </c>
     </row>
-    <row r="115" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>559</v>
       </c>
@@ -35615,7 +35614,7 @@
         <v>787133.2</v>
       </c>
     </row>
-    <row r="116" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A116" s="7" t="s">
         <v>563</v>
       </c>
@@ -35864,7 +35863,7 @@
         <v>787134.2</v>
       </c>
     </row>
-    <row r="117" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>567</v>
       </c>
@@ -36109,7 +36108,7 @@
         <v>787135.2</v>
       </c>
     </row>
-    <row r="118" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
         <v>571</v>
       </c>
@@ -36358,7 +36357,7 @@
         <v>787136.2</v>
       </c>
     </row>
-    <row r="119" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>575</v>
       </c>
@@ -36607,7 +36606,7 @@
         <v>787137.2</v>
       </c>
     </row>
-    <row r="120" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
         <v>579</v>
       </c>
@@ -36856,7 +36855,7 @@
         <v>787138.2</v>
       </c>
     </row>
-    <row r="121" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A121" s="7" t="s">
         <v>583</v>
       </c>
@@ -37105,7 +37104,7 @@
         <v>787139.2</v>
       </c>
     </row>
-    <row r="122" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A122" s="7" t="s">
         <v>589</v>
       </c>
@@ -37354,7 +37353,7 @@
         <v>787140.2</v>
       </c>
     </row>
-    <row r="123" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>595</v>
       </c>
@@ -37599,7 +37598,7 @@
         <v>787141.2</v>
       </c>
     </row>
-    <row r="124" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>600</v>
       </c>
@@ -37846,7 +37845,7 @@
         <v>787142.2</v>
       </c>
     </row>
-    <row r="125" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A125" s="7" t="s">
         <v>604</v>
       </c>
@@ -38089,7 +38088,7 @@
         <v>787143.2</v>
       </c>
     </row>
-    <row r="126" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>607</v>
       </c>
@@ -38336,7 +38335,7 @@
         <v>787144.2</v>
       </c>
     </row>
-    <row r="127" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A127" s="7" t="s">
         <v>610</v>
       </c>
@@ -38585,7 +38584,7 @@
         <v>787145.2</v>
       </c>
     </row>
-    <row r="128" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>615</v>
       </c>
@@ -38830,7 +38829,7 @@
         <v>787146.2</v>
       </c>
     </row>
-    <row r="129" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>618</v>
       </c>
@@ -39091,7 +39090,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="130" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A130" s="7" t="s">
         <v>622</v>
       </c>
@@ -39340,7 +39339,7 @@
         <v>787148.2</v>
       </c>
     </row>
-    <row r="131" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>627</v>
       </c>
@@ -39589,7 +39588,7 @@
         <v>787149.2</v>
       </c>
     </row>
-    <row r="132" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A132" s="7" t="s">
         <v>631</v>
       </c>
@@ -39836,7 +39835,7 @@
         <v>787150.2</v>
       </c>
     </row>
-    <row r="133" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A133" s="7" t="s">
         <v>635</v>
       </c>
@@ -40097,7 +40096,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="134" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>641</v>
       </c>
@@ -40346,7 +40345,7 @@
         <v>787152.2</v>
       </c>
     </row>
-    <row r="135" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A135" s="7" t="s">
         <v>645</v>
       </c>
@@ -40589,7 +40588,7 @@
         <v>787153.2</v>
       </c>
     </row>
-    <row r="136" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A136" s="7" t="s">
         <v>650</v>
       </c>
@@ -40838,7 +40837,7 @@
         <v>787154.2</v>
       </c>
     </row>
-    <row r="137" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>655</v>
       </c>
@@ -41087,7 +41086,7 @@
         <v>787155.2</v>
       </c>
     </row>
-    <row r="138" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A138" s="7" t="s">
         <v>660</v>
       </c>
@@ -41334,7 +41333,7 @@
         <v>787156.2</v>
       </c>
     </row>
-    <row r="139" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>664</v>
       </c>
@@ -41583,7 +41582,7 @@
         <v>787157.2</v>
       </c>
     </row>
-    <row r="140" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A140" s="7" t="s">
         <v>669</v>
       </c>
@@ -41832,7 +41831,7 @@
         <v>787158.2</v>
       </c>
     </row>
-    <row r="141" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>673</v>
       </c>
@@ -42079,7 +42078,7 @@
         <v>787159.2</v>
       </c>
     </row>
-    <row r="142" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>677</v>
       </c>
@@ -42320,7 +42319,7 @@
         <v>787160.2</v>
       </c>
     </row>
-    <row r="143" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A143" s="7" t="s">
         <v>682</v>
       </c>
@@ -42567,7 +42566,7 @@
         <v>787161.2</v>
       </c>
     </row>
-    <row r="144" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>687</v>
       </c>
@@ -42814,7 +42813,7 @@
         <v>787162.2</v>
       </c>
     </row>
-    <row r="145" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A145" s="7" t="s">
         <v>691</v>
       </c>
@@ -43061,7 +43060,7 @@
         <v>787163.2</v>
       </c>
     </row>
-    <row r="146" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>695</v>
       </c>
@@ -43310,7 +43309,7 @@
         <v>787164.2</v>
       </c>
     </row>
-    <row r="147" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A147" s="7" t="s">
         <v>700</v>
       </c>
@@ -43559,7 +43558,7 @@
         <v>787165.2</v>
       </c>
     </row>
-    <row r="148" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>704</v>
       </c>
@@ -43808,7 +43807,7 @@
         <v>787166.2</v>
       </c>
     </row>
-    <row r="149" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A149" s="7" t="s">
         <v>708</v>
       </c>
@@ -44057,7 +44056,7 @@
         <v>787167.2</v>
       </c>
     </row>
-    <row r="150" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A150" s="7" t="s">
         <v>713</v>
       </c>
@@ -44304,7 +44303,7 @@
         <v>787168.2</v>
       </c>
     </row>
-    <row r="151" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A151" s="7" t="s">
         <v>718</v>
       </c>
@@ -44551,7 +44550,7 @@
         <v>787169.2</v>
       </c>
     </row>
-    <row r="152" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A152" s="7" t="s">
         <v>722</v>
       </c>
@@ -44800,7 +44799,7 @@
         <v>787170.2</v>
       </c>
     </row>
-    <row r="153" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>726</v>
       </c>
@@ -45049,7 +45048,7 @@
         <v>787171.2</v>
       </c>
     </row>
-    <row r="154" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A154" s="7" t="s">
         <v>732</v>
       </c>
@@ -45294,7 +45293,7 @@
         <v>787172.2</v>
       </c>
     </row>
-    <row r="155" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>736</v>
       </c>
@@ -45541,7 +45540,7 @@
         <v>787173.2</v>
       </c>
     </row>
-    <row r="156" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A156" s="7" t="s">
         <v>739</v>
       </c>
@@ -45788,7 +45787,7 @@
         <v>787174.2</v>
       </c>
     </row>
-    <row r="157" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>742</v>
       </c>
@@ -46037,7 +46036,7 @@
         <v>787175.2</v>
       </c>
     </row>
-    <row r="158" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A158" s="7" t="s">
         <v>746</v>
       </c>
@@ -46284,7 +46283,7 @@
         <v>787176.2</v>
       </c>
     </row>
-    <row r="159" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A159" s="7" t="s">
         <v>749</v>
       </c>
@@ -46533,7 +46532,7 @@
         <v>787177.2</v>
       </c>
     </row>
-    <row r="160" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A160" s="7" t="s">
         <v>753</v>
       </c>
@@ -46780,7 +46779,7 @@
         <v>787178.2</v>
       </c>
     </row>
-    <row r="161" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>756</v>
       </c>
@@ -47027,7 +47026,7 @@
         <v>787179.2</v>
       </c>
     </row>
-    <row r="162" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A162" s="7" t="s">
         <v>761</v>
       </c>
@@ -47274,7 +47273,7 @@
         <v>787180.2</v>
       </c>
     </row>
-    <row r="163" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>766</v>
       </c>
@@ -47535,7 +47534,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="164" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A164" s="7" t="s">
         <v>771</v>
       </c>
@@ -47784,7 +47783,7 @@
         <v>787182.2</v>
       </c>
     </row>
-    <row r="165" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>775</v>
       </c>
@@ -48029,7 +48028,7 @@
         <v>787183.2</v>
       </c>
     </row>
-    <row r="166" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A166" s="7" t="s">
         <v>779</v>
       </c>
@@ -48274,7 +48273,7 @@
         <v>787184.2</v>
       </c>
     </row>
-    <row r="167" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A167" s="7" t="s">
         <v>783</v>
       </c>
@@ -48535,7 +48534,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="168" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>788</v>
       </c>
@@ -48784,7 +48783,7 @@
         <v>787186.2</v>
       </c>
     </row>
-    <row r="169" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A169" s="7" t="s">
         <v>793</v>
       </c>
@@ -49045,7 +49044,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="170" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A170" s="7" t="s">
         <v>797</v>
       </c>
@@ -49294,7 +49293,7 @@
         <v>787188.2</v>
       </c>
     </row>
-    <row r="171" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A171" s="7" t="s">
         <v>801</v>
       </c>
@@ -49555,7 +49554,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="172" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>806</v>
       </c>
@@ -49804,7 +49803,7 @@
         <v>787190.2</v>
       </c>
     </row>
-    <row r="173" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A173" s="7" t="s">
         <v>811</v>
       </c>
@@ -50051,7 +50050,7 @@
         <v>787191.2</v>
       </c>
     </row>
-    <row r="174" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>815</v>
       </c>
@@ -50300,7 +50299,7 @@
         <v>787192.2</v>
       </c>
     </row>
-    <row r="175" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A175" s="7" t="s">
         <v>819</v>
       </c>
@@ -50545,7 +50544,7 @@
         <v>787193.2</v>
       </c>
     </row>
-    <row r="176" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A176" s="7" t="s">
         <v>823</v>
       </c>
@@ -50806,7 +50805,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="177" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A177" s="7" t="s">
         <v>828</v>
       </c>
@@ -51055,7 +51054,7 @@
         <v>787195.2</v>
       </c>
     </row>
-    <row r="178" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>833</v>
       </c>
@@ -51316,7 +51315,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="179" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A179" s="7" t="s">
         <v>837</v>
       </c>
@@ -51577,7 +51576,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="180" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>841</v>
       </c>
@@ -51826,7 +51825,7 @@
         <v>787198.2</v>
       </c>
     </row>
-    <row r="181" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A181" s="7" t="s">
         <v>846</v>
       </c>
@@ -52071,7 +52070,7 @@
         <v>787199.2</v>
       </c>
     </row>
-    <row r="182" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>850</v>
       </c>
@@ -52320,7 +52319,7 @@
         <v>787200.2</v>
       </c>
     </row>
-    <row r="183" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A183" s="7" t="s">
         <v>854</v>
       </c>
@@ -52565,7 +52564,7 @@
         <v>787201.2</v>
       </c>
     </row>
-    <row r="184" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>859</v>
       </c>
@@ -52814,7 +52813,7 @@
         <v>787202.2</v>
       </c>
     </row>
-    <row r="185" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>863</v>
       </c>
@@ -53063,7 +53062,7 @@
         <v>787203.2</v>
       </c>
     </row>
-    <row r="186" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>869</v>
       </c>
@@ -53310,7 +53309,7 @@
         <v>787204.2</v>
       </c>
     </row>
-    <row r="187" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A187" s="7" t="s">
         <v>874</v>
       </c>
@@ -53559,7 +53558,7 @@
         <v>787205.2</v>
       </c>
     </row>
-    <row r="188" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A188" s="7" t="s">
         <v>878</v>
       </c>
@@ -53808,7 +53807,7 @@
         <v>787206.2</v>
       </c>
     </row>
-    <row r="189" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>882</v>
       </c>
@@ -54057,7 +54056,7 @@
         <v>787207.2</v>
       </c>
     </row>
-    <row r="190" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A190" s="7" t="s">
         <v>886</v>
       </c>
@@ -54304,7 +54303,7 @@
         <v>787208.2</v>
       </c>
     </row>
-    <row r="191" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>890</v>
       </c>
@@ -54553,7 +54552,7 @@
         <v>787209.2</v>
       </c>
     </row>
-    <row r="192" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>894</v>
       </c>
@@ -54814,7 +54813,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="193" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A193" s="7" t="s">
         <v>898</v>
       </c>
@@ -55057,7 +55056,7 @@
         <v>787211.2</v>
       </c>
     </row>
-    <row r="194" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>903</v>
       </c>
@@ -55306,7 +55305,7 @@
         <v>787212.2</v>
       </c>
     </row>
-    <row r="195" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A195" s="7" t="s">
         <v>907</v>
       </c>
@@ -55555,7 +55554,7 @@
         <v>787213.2</v>
       </c>
     </row>
-    <row r="196" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>911</v>
       </c>
@@ -55802,7 +55801,7 @@
         <v>787214.2</v>
       </c>
     </row>
-    <row r="197" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A197" s="7" t="s">
         <v>915</v>
       </c>
@@ -56051,7 +56050,7 @@
         <v>787215.2</v>
       </c>
     </row>
-    <row r="198" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>920</v>
       </c>
@@ -56300,7 +56299,7 @@
         <v>787216.2</v>
       </c>
     </row>
-    <row r="199" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>925</v>
       </c>
@@ -56547,7 +56546,7 @@
         <v>787217.2</v>
       </c>
     </row>
-    <row r="200" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>930</v>
       </c>
@@ -56788,7 +56787,7 @@
         <v>787218.2</v>
       </c>
     </row>
-    <row r="201" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A201" s="7" t="s">
         <v>936</v>
       </c>
@@ -57037,7 +57036,7 @@
         <v>787219.2</v>
       </c>
     </row>
-    <row r="202" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>940</v>
       </c>
@@ -57284,7 +57283,7 @@
         <v>787220.2</v>
       </c>
     </row>
-    <row r="203" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A203" s="7" t="s">
         <v>944</v>
       </c>
@@ -57531,7 +57530,7 @@
         <v>787221.2</v>
       </c>
     </row>
-    <row r="204" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>948</v>
       </c>
@@ -57780,7 +57779,7 @@
         <v>787222.2</v>
       </c>
     </row>
-    <row r="205" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A205" s="7" t="s">
         <v>952</v>
       </c>
@@ -58029,7 +58028,7 @@
         <v>787223.2</v>
       </c>
     </row>
-    <row r="206" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A206" s="7" t="s">
         <v>957</v>
       </c>
@@ -58278,7 +58277,7 @@
         <v>787224.2</v>
       </c>
     </row>
-    <row r="207" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A207" s="7" t="s">
         <v>963</v>
       </c>
@@ -58527,7 +58526,7 @@
         <v>787225.2</v>
       </c>
     </row>
-    <row r="208" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>967</v>
       </c>
@@ -58776,7 +58775,7 @@
         <v>787226.2</v>
       </c>
     </row>
-    <row r="209" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A209" s="7" t="s">
         <v>971</v>
       </c>
@@ -59023,7 +59022,7 @@
         <v>787227.2</v>
       </c>
     </row>
-    <row r="210" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>977</v>
       </c>
@@ -59519,7 +59518,7 @@
         <v>787229.2</v>
       </c>
     </row>
-    <row r="212" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A212" s="7" t="s">
         <v>986</v>
       </c>
@@ -59778,7 +59777,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="213" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>991</v>
       </c>
@@ -60027,7 +60026,7 @@
         <v>787231.2</v>
       </c>
     </row>
-    <row r="214" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A214" s="7" t="s">
         <v>999</v>
       </c>
@@ -60276,7 +60275,7 @@
         <v>787232.2</v>
       </c>
     </row>
-    <row r="215" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>1005</v>
       </c>
@@ -60525,7 +60524,7 @@
         <v>787233.2</v>
       </c>
     </row>
-    <row r="216" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A216" s="7" t="s">
         <v>1009</v>
       </c>
@@ -60774,7 +60773,7 @@
         <v>787234.2</v>
       </c>
     </row>
-    <row r="217" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>1013</v>
       </c>
@@ -61023,7 +61022,7 @@
         <v>787235.2</v>
       </c>
     </row>
-    <row r="218" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A218" s="7" t="s">
         <v>1017</v>
       </c>
@@ -61272,7 +61271,7 @@
         <v>787236.2</v>
       </c>
     </row>
-    <row r="219" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A219" s="7" t="s">
         <v>1021</v>
       </c>
@@ -61776,7 +61775,7 @@
         <v>787238.2</v>
       </c>
     </row>
-    <row r="221" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A221" s="7" t="s">
         <v>1030</v>
       </c>
@@ -62025,7 +62024,7 @@
         <v>787239.2</v>
       </c>
     </row>
-    <row r="222" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>1033</v>
       </c>
@@ -62286,7 +62285,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="223" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A223" s="7" t="s">
         <v>1037</v>
       </c>
@@ -62543,7 +62542,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="224" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>1041</v>
       </c>
@@ -62788,7 +62787,7 @@
         <v>787242.2</v>
       </c>
     </row>
-    <row r="225" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A225" s="7" t="s">
         <v>1046</v>
       </c>
@@ -63049,7 +63048,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="226" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>1051</v>
       </c>
@@ -63310,7 +63309,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="227" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A227" s="7" t="s">
         <v>1055</v>
       </c>
@@ -63571,7 +63570,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="228" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A228" s="7" t="s">
         <v>1059</v>
       </c>
@@ -63832,7 +63831,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="229" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>1063</v>
       </c>
@@ -64093,7 +64092,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="230" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A230" s="7" t="s">
         <v>1067</v>
       </c>
@@ -64354,7 +64353,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="231" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>1072</v>
       </c>
@@ -64613,7 +64612,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="232" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>1076</v>
       </c>
@@ -64862,7 +64861,7 @@
         <v>787250.2</v>
       </c>
     </row>
-    <row r="233" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A233" s="7" t="s">
         <v>1080</v>
       </c>
@@ -65119,7 +65118,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="234" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>1087</v>
       </c>
@@ -65380,7 +65379,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="235" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>1091</v>
       </c>
@@ -65629,7 +65628,7 @@
         <v>787253.2</v>
       </c>
     </row>
-    <row r="236" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A236" s="7" t="s">
         <v>1095</v>
       </c>
@@ -65878,7 +65877,7 @@
         <v>787254.2</v>
       </c>
     </row>
-    <row r="237" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>1099</v>
       </c>
@@ -66127,7 +66126,7 @@
         <v>787255.2</v>
       </c>
     </row>
-    <row r="238" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A238" s="7" t="s">
         <v>1103</v>
       </c>
@@ -66376,7 +66375,7 @@
         <v>787256.2</v>
       </c>
     </row>
-    <row r="239" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>1107</v>
       </c>
@@ -66621,7 +66620,7 @@
         <v>787257.2</v>
       </c>
     </row>
-    <row r="240" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A240" s="7" t="s">
         <v>1111</v>
       </c>
@@ -66870,7 +66869,7 @@
         <v>787258.2</v>
       </c>
     </row>
-    <row r="241" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A241" s="7" t="s">
         <v>1116</v>
       </c>
@@ -67115,7 +67114,7 @@
         <v>787259.2</v>
       </c>
     </row>
-    <row r="242" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>1124</v>
       </c>
@@ -67364,7 +67363,7 @@
         <v>787260.2</v>
       </c>
     </row>
-    <row r="243" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A243" s="7" t="s">
         <v>1130</v>
       </c>
@@ -67613,7 +67612,7 @@
         <v>787261.2</v>
       </c>
     </row>
-    <row r="244" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>1134</v>
       </c>
@@ -67860,7 +67859,7 @@
         <v>787262.2</v>
       </c>
     </row>
-    <row r="245" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A245" s="7" t="s">
         <v>1138</v>
       </c>
@@ -68109,7 +68108,7 @@
         <v>787263.2</v>
       </c>
     </row>
-    <row r="246" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>1142</v>
       </c>
@@ -68358,7 +68357,7 @@
         <v>787264.2</v>
       </c>
     </row>
-    <row r="247" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A247" s="7" t="s">
         <v>1147</v>
       </c>
@@ -68852,7 +68851,7 @@
         <v>787266.2</v>
       </c>
     </row>
-    <row r="249" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>1156</v>
       </c>
@@ -69113,7 +69112,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="250" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>1160</v>
       </c>
@@ -69362,7 +69361,7 @@
         <v>787268.2</v>
       </c>
     </row>
-    <row r="251" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A251" s="7" t="s">
         <v>1165</v>
       </c>
@@ -69605,7 +69604,7 @@
         <v>787269.2</v>
       </c>
     </row>
-    <row r="252" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>1169</v>
       </c>
@@ -69854,7 +69853,7 @@
         <v>787270.2</v>
       </c>
     </row>
-    <row r="253" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A253" s="7" t="s">
         <v>1173</v>
       </c>
@@ -70103,7 +70102,7 @@
         <v>787271.2</v>
       </c>
     </row>
-    <row r="254" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>1177</v>
       </c>
@@ -70350,7 +70349,7 @@
         <v>787272.2</v>
       </c>
     </row>
-    <row r="255" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A255" s="7" t="s">
         <v>1181</v>
       </c>
@@ -70599,7 +70598,7 @@
         <v>787273.2</v>
       </c>
     </row>
-    <row r="256" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A256" s="2" t="s">
         <v>1185</v>
       </c>
@@ -70848,7 +70847,7 @@
         <v>787274.2</v>
       </c>
     </row>
-    <row r="257" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A257" s="7" t="s">
         <v>1189</v>
       </c>
@@ -71095,7 +71094,7 @@
         <v>787275.2</v>
       </c>
     </row>
-    <row r="258" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A258" s="2" t="s">
         <v>1196</v>
       </c>
@@ -71334,7 +71333,7 @@
         <v>787276.2</v>
       </c>
     </row>
-    <row r="259" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>1201</v>
       </c>
@@ -71583,7 +71582,7 @@
         <v>787277.2</v>
       </c>
     </row>
-    <row r="260" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>1207</v>
       </c>
@@ -71830,7 +71829,7 @@
         <v>787278.2</v>
       </c>
     </row>
-    <row r="261" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A261" s="7" t="s">
         <v>1189</v>
       </c>
@@ -72089,7 +72088,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="262" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A262" s="2" t="s">
         <v>1196</v>
       </c>
@@ -72340,7 +72339,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="263" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A263" s="2" t="s">
         <v>1201</v>
       </c>
@@ -72601,7 +72600,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="264" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A264" s="2" t="s">
         <v>1207</v>
       </c>
@@ -72860,7 +72859,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="265" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A265" s="2" t="s">
         <v>405</v>
       </c>
@@ -73113,7 +73112,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="266" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>405</v>
       </c>
@@ -73366,7 +73365,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="267" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>405</v>
       </c>
@@ -73619,7 +73618,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="268" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>405</v>
       </c>
@@ -73872,7 +73871,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="269" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>405</v>
       </c>
@@ -74125,7 +74124,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="270" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
         <v>405</v>
       </c>
@@ -74378,7 +74377,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="271" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>405</v>
       </c>
@@ -74631,7 +74630,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="272" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>405</v>
       </c>
@@ -74884,7 +74883,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="273" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>405</v>
       </c>
@@ -75137,7 +75136,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="274" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>405</v>
       </c>
@@ -75390,7 +75389,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="275" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>405</v>
       </c>
@@ -79420,7 +79419,7 @@
         <v>787266.2</v>
       </c>
     </row>
-    <row r="291" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
         <v>405</v>
       </c>
@@ -79673,7 +79672,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="292" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>405</v>
       </c>
@@ -79926,7 +79925,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="293" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
         <v>405</v>
       </c>
@@ -80179,7 +80178,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="294" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
         <v>405</v>
       </c>
@@ -80432,7 +80431,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="295" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
         <v>405</v>
       </c>
@@ -80685,7 +80684,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="296" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
         <v>405</v>
       </c>
@@ -80938,7 +80937,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="297" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>405</v>
       </c>
@@ -81191,7 +81190,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="298" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>405</v>
       </c>
@@ -81444,7 +81443,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="299" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>405</v>
       </c>
@@ -81644,7 +81643,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="300" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
         <v>405</v>
       </c>
@@ -81844,7 +81843,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="301" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
         <v>405</v>
       </c>
@@ -82044,7 +82043,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="302" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A302" s="2" t="s">
         <v>405</v>
       </c>
@@ -82244,7 +82243,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="303" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A303" s="2" t="s">
         <v>405</v>
       </c>
@@ -82444,7 +82443,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="304" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A304" s="2" t="s">
         <v>405</v>
       </c>
@@ -82644,7 +82643,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="305" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
         <v>405</v>
       </c>
@@ -82844,7 +82843,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="306" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A306" s="2" t="s">
         <v>405</v>
       </c>
@@ -88183,13 +88182,7 @@
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A258:N258 A262:F262 H262:N262" name="All Access Jorge H_98" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A259:N259 A263:F263 H263:N263" name="All Access Jorge H_99" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
   </protectedRanges>
-  <autoFilter ref="A1:CK306" xr:uid="{5A45D9DC-E8AF-436A-91D0-388125A4A950}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="Cerrado"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:CK326" xr:uid="{5A45D9DC-E8AF-436A-91D0-388125A4A950}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
